--- a/Pittsburgh WIP Data/WIP Data Import Template.xlsx
+++ b/Pittsburgh WIP Data/WIP Data Import Template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29825"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pittsburghlab05\OneDrive - SPL\Dev\Pitt Lab WIP Dashboard\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://spllabs-my.sharepoint.com/personal/jonathan_john_spl-inc_com/Documents/Dev/Pitt Lab WIP Dashboard/Pittsburgh WIP Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_E9006845ED4581FB0A9CD559D460A3FB778B3E7F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="11_E9006845ED4581FB0A9CD559D460A3FB778B3E7F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{689D8F30-B208-4E02-93B6-991B3225C2F1}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="-105" windowWidth="23250" windowHeight="13890" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="588" uniqueCount="127">
   <si>
     <t>Due Days</t>
   </si>
@@ -73,13 +73,346 @@
   </si>
   <si>
     <t>Column 1</t>
+  </si>
+  <si>
+    <t>005A</t>
+  </si>
+  <si>
+    <t>EOG22</t>
+  </si>
+  <si>
+    <t>Oil</t>
+  </si>
+  <si>
+    <t>EOS-VP</t>
+  </si>
+  <si>
+    <t>001A</t>
+  </si>
+  <si>
+    <t>Cylinder piston 500cc</t>
+  </si>
+  <si>
+    <t>2500-00873</t>
+  </si>
+  <si>
+    <t>GC-C10LIQ</t>
+  </si>
+  <si>
+    <t>WILLIAMS</t>
+  </si>
+  <si>
+    <t>Liquid</t>
+  </si>
+  <si>
+    <t>Report sent 3.12.2026</t>
+  </si>
+  <si>
+    <t>GC-C6GAS</t>
+  </si>
+  <si>
+    <t>002A</t>
+  </si>
+  <si>
+    <t>ENERGY-TRA-LA-GRA</t>
+  </si>
+  <si>
+    <t>Cylinder 300cc</t>
+  </si>
+  <si>
+    <t>1111-013068</t>
+  </si>
+  <si>
+    <t>Gas</t>
+  </si>
+  <si>
+    <t>003A</t>
+  </si>
+  <si>
+    <t>1111-010246</t>
+  </si>
+  <si>
+    <t>004A</t>
+  </si>
+  <si>
+    <t>1111-010813</t>
+  </si>
+  <si>
+    <t>1111-012940</t>
+  </si>
+  <si>
+    <t>006A</t>
+  </si>
+  <si>
+    <t>1111-013139</t>
+  </si>
+  <si>
+    <t>007A</t>
+  </si>
+  <si>
+    <t>3040-02216</t>
+  </si>
+  <si>
+    <t>008A</t>
+  </si>
+  <si>
+    <t>1111-013119</t>
+  </si>
+  <si>
+    <t>009A</t>
+  </si>
+  <si>
+    <t>1111-012534</t>
+  </si>
+  <si>
+    <t>010A</t>
+  </si>
+  <si>
+    <t>1030-06410</t>
+  </si>
+  <si>
+    <t>011A</t>
+  </si>
+  <si>
+    <t>1111-012561</t>
+  </si>
+  <si>
+    <t>012A</t>
+  </si>
+  <si>
+    <t>1111-013178</t>
+  </si>
+  <si>
+    <t>013A</t>
+  </si>
+  <si>
+    <t>4030-004581</t>
+  </si>
+  <si>
+    <t>014A</t>
+  </si>
+  <si>
+    <t>1111-010717</t>
+  </si>
+  <si>
+    <t>015A</t>
+  </si>
+  <si>
+    <t>3040-05219</t>
+  </si>
+  <si>
+    <t>016A</t>
+  </si>
+  <si>
+    <t>9050-00336</t>
+  </si>
+  <si>
+    <t>017A</t>
+  </si>
+  <si>
+    <t>1111-013142</t>
+  </si>
+  <si>
+    <t>018A</t>
+  </si>
+  <si>
+    <t>1111-010224</t>
+  </si>
+  <si>
+    <t>019A</t>
+  </si>
+  <si>
+    <t>1111-010723</t>
+  </si>
+  <si>
+    <t>020A</t>
+  </si>
+  <si>
+    <t>1111-013136</t>
+  </si>
+  <si>
+    <t>021A</t>
+  </si>
+  <si>
+    <t>1111-010657</t>
+  </si>
+  <si>
+    <t>022A</t>
+  </si>
+  <si>
+    <t>1111-013034</t>
+  </si>
+  <si>
+    <t>023A</t>
+  </si>
+  <si>
+    <t>1111-012464</t>
+  </si>
+  <si>
+    <t>024A</t>
+  </si>
+  <si>
+    <t>1111-010710</t>
+  </si>
+  <si>
+    <t>025A</t>
+  </si>
+  <si>
+    <t>1111-010840</t>
+  </si>
+  <si>
+    <t>1111-010233</t>
+  </si>
+  <si>
+    <t>1111-012458</t>
+  </si>
+  <si>
+    <t>1111-013193</t>
+  </si>
+  <si>
+    <t>1111-012453</t>
+  </si>
+  <si>
+    <t>1111-012499</t>
+  </si>
+  <si>
+    <t>1111-010790</t>
+  </si>
+  <si>
+    <t>1111-012501</t>
+  </si>
+  <si>
+    <t>1111-012498</t>
+  </si>
+  <si>
+    <t>1111-012490</t>
+  </si>
+  <si>
+    <t>1111-010691</t>
+  </si>
+  <si>
+    <t>1111-010220</t>
+  </si>
+  <si>
+    <t>1111-012509</t>
+  </si>
+  <si>
+    <t>1111-013146</t>
+  </si>
+  <si>
+    <t>1111-013023</t>
+  </si>
+  <si>
+    <t>1111-010228</t>
+  </si>
+  <si>
+    <t>1111-010663</t>
+  </si>
+  <si>
+    <t>1111-010232</t>
+  </si>
+  <si>
+    <t>1111-010218</t>
+  </si>
+  <si>
+    <t>1111-014968</t>
+  </si>
+  <si>
+    <t>1111-012292</t>
+  </si>
+  <si>
+    <t>1111-001012</t>
+  </si>
+  <si>
+    <t>1111-004877</t>
+  </si>
+  <si>
+    <t>1111-008907</t>
+  </si>
+  <si>
+    <t>4030-02071</t>
+  </si>
+  <si>
+    <t>4030-004851</t>
+  </si>
+  <si>
+    <t>1111-012788</t>
+  </si>
+  <si>
+    <t>3040-05882</t>
+  </si>
+  <si>
+    <t>1030-06088</t>
+  </si>
+  <si>
+    <t>3040-02912</t>
+  </si>
+  <si>
+    <t>1111-013118</t>
+  </si>
+  <si>
+    <t>1111-010837</t>
+  </si>
+  <si>
+    <t>1111-003806</t>
+  </si>
+  <si>
+    <t>1111-013120</t>
+  </si>
+  <si>
+    <t>Cylinder 500cc</t>
+  </si>
+  <si>
+    <t>1111-006618</t>
+  </si>
+  <si>
+    <t>1111-009918</t>
+  </si>
+  <si>
+    <t>1030-07937</t>
+  </si>
+  <si>
+    <t>1030-07953</t>
+  </si>
+  <si>
+    <t>1030-08110</t>
+  </si>
+  <si>
+    <t>1111-002069</t>
+  </si>
+  <si>
+    <t>1111-003409</t>
+  </si>
+  <si>
+    <t>1111-009236</t>
+  </si>
+  <si>
+    <t>3040-02823</t>
+  </si>
+  <si>
+    <t>1030-06668</t>
+  </si>
+  <si>
+    <t>1111-007318</t>
+  </si>
+  <si>
+    <t>4030-006037</t>
+  </si>
+  <si>
+    <t>OHIO-GAT-COM</t>
+  </si>
+  <si>
+    <t>Could not clearly read sample temp on tag</t>
+  </si>
+  <si>
+    <t>026A</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -113,13 +446,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -387,19 +726,20 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:Q9"/>
-  <sheetFormatPr defaultColWidth="12.7109375" defaultRowHeight="15.75" customHeight="1"/>
+  <dimension ref="A1:Q101"/>
+  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="15.28515625" customWidth="1"/>
-    <col min="3" max="3" width="13.7109375" customWidth="1"/>
-    <col min="5" max="5" width="18.42578125" customWidth="1"/>
-    <col min="10" max="10" width="18.28515625" customWidth="1"/>
-    <col min="11" max="11" width="12.85546875" customWidth="1"/>
-    <col min="13" max="13" width="13.42578125" customWidth="1"/>
-    <col min="14" max="14" width="37.7109375" customWidth="1"/>
+    <col min="2" max="2" width="15.33203125" customWidth="1"/>
+    <col min="3" max="3" width="13.6640625" customWidth="1"/>
+    <col min="5" max="5" width="18.44140625" customWidth="1"/>
+    <col min="10" max="10" width="18.33203125" customWidth="1"/>
+    <col min="11" max="11" width="12.88671875" customWidth="1"/>
+    <col min="13" max="13" width="13.44140625" customWidth="1"/>
+    <col min="14" max="14" width="37.6640625" customWidth="1"/>
+    <col min="15" max="15" width="19.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="22.5" customHeight="1">
+    <row r="1" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -449,29 +789,4505 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:17" ht="15.75" customHeight="1">
+    <row r="2" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2"/>
-    </row>
-    <row r="3" spans="1:17" ht="15.75" customHeight="1">
+      <c r="B2" s="3">
+        <v>-6</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" s="3">
+        <v>26031372</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G2" s="4">
+        <v>46094</v>
+      </c>
+      <c r="H2" s="4">
+        <v>46094</v>
+      </c>
+      <c r="I2" s="4">
+        <v>46097</v>
+      </c>
+      <c r="J2" s="3">
+        <v>3</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="N2" s="3"/>
+      <c r="O2" s="3"/>
+      <c r="P2" s="3"/>
+      <c r="Q2" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2"/>
-    </row>
-    <row r="4" spans="1:17" ht="15.75" customHeight="1">
+      <c r="B3" s="3">
+        <v>-6</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" s="3">
+        <v>26031372</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G3" s="4">
+        <v>46094</v>
+      </c>
+      <c r="H3" s="4">
+        <v>46094</v>
+      </c>
+      <c r="I3" s="4">
+        <v>46097</v>
+      </c>
+      <c r="J3" s="3">
+        <v>3</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="N3" s="3"/>
+      <c r="O3" s="3"/>
+      <c r="P3" s="3"/>
+      <c r="Q3" s="3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2"/>
-    </row>
-    <row r="5" spans="1:17" ht="15.75" customHeight="1">
+      <c r="B4" s="3">
+        <v>-4</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" s="3">
+        <v>26031154</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G4" s="4">
+        <v>46092</v>
+      </c>
+      <c r="H4" s="4">
+        <v>46093</v>
+      </c>
+      <c r="I4" s="4">
+        <v>46099</v>
+      </c>
+      <c r="J4" s="3">
+        <v>3</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L4" s="3">
+        <v>95402</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="N4" s="3"/>
+      <c r="O4" s="3"/>
+      <c r="P4" s="3"/>
+      <c r="Q4" s="3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2"/>
-    </row>
-    <row r="6" spans="1:17" ht="15.75" customHeight="1">
+      <c r="B5" s="3">
+        <v>-4</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D5" s="3">
+        <v>26031155</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G5" s="4">
+        <v>46092</v>
+      </c>
+      <c r="H5" s="4">
+        <v>46093</v>
+      </c>
+      <c r="I5" s="4">
+        <v>46099</v>
+      </c>
+      <c r="J5" s="3">
+        <v>3</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L5" s="3">
+        <v>96237</v>
+      </c>
+      <c r="M5" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="N5" s="3"/>
+      <c r="O5" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="P5" s="3"/>
+      <c r="Q5" s="3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2"/>
-    </row>
-    <row r="7" spans="1:17" ht="15.75" customHeight="1">
+      <c r="B6" s="3">
+        <v>-5</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D6" s="3">
+        <v>26030964</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G6" s="4">
+        <v>46090</v>
+      </c>
+      <c r="H6" s="4">
+        <v>46091</v>
+      </c>
+      <c r="I6" s="4">
+        <v>46098</v>
+      </c>
+      <c r="J6" s="3">
+        <v>3</v>
+      </c>
+      <c r="K6" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="L6" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="M6" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="N6" s="3"/>
+      <c r="O6" s="3"/>
+      <c r="P6" s="3"/>
+      <c r="Q6" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2"/>
-    </row>
-    <row r="8" spans="1:17" ht="15.75" customHeight="1">
+      <c r="B7" s="3">
+        <v>-5</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D7" s="3">
+        <v>26030964</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G7" s="4">
+        <v>46090</v>
+      </c>
+      <c r="H7" s="4">
+        <v>46091</v>
+      </c>
+      <c r="I7" s="4">
+        <v>46098</v>
+      </c>
+      <c r="J7" s="3">
+        <v>3</v>
+      </c>
+      <c r="K7" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="L7" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="M7" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="N7" s="3"/>
+      <c r="O7" s="3"/>
+      <c r="P7" s="3"/>
+      <c r="Q7" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2"/>
-    </row>
-    <row r="9" spans="1:17" ht="15.75" customHeight="1">
+      <c r="B8" s="3">
+        <v>-5</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D8" s="3">
+        <v>26030964</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G8" s="4">
+        <v>46090</v>
+      </c>
+      <c r="H8" s="4">
+        <v>46091</v>
+      </c>
+      <c r="I8" s="4">
+        <v>46098</v>
+      </c>
+      <c r="J8" s="3">
+        <v>3</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="M8" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="N8" s="3"/>
+      <c r="O8" s="3"/>
+      <c r="P8" s="3"/>
+      <c r="Q8" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2"/>
+      <c r="B9" s="3">
+        <v>-5</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D9" s="3">
+        <v>26030964</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G9" s="4">
+        <v>46090</v>
+      </c>
+      <c r="H9" s="4">
+        <v>46091</v>
+      </c>
+      <c r="I9" s="4">
+        <v>46098</v>
+      </c>
+      <c r="J9" s="3">
+        <v>3</v>
+      </c>
+      <c r="K9" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="L9" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="N9" s="3"/>
+      <c r="O9" s="3"/>
+      <c r="P9" s="3"/>
+      <c r="Q9" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="2"/>
+      <c r="B10" s="3">
+        <v>-5</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D10" s="3">
+        <v>26030964</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G10" s="4">
+        <v>46090</v>
+      </c>
+      <c r="H10" s="4">
+        <v>46091</v>
+      </c>
+      <c r="I10" s="4">
+        <v>46098</v>
+      </c>
+      <c r="J10" s="3">
+        <v>3</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="L10" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M10" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="N10" s="3"/>
+      <c r="O10" s="3"/>
+      <c r="P10" s="3"/>
+      <c r="Q10" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="2"/>
+      <c r="B11" s="3">
+        <v>-5</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D11" s="3">
+        <v>26030964</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G11" s="4">
+        <v>46090</v>
+      </c>
+      <c r="H11" s="4">
+        <v>46091</v>
+      </c>
+      <c r="I11" s="4">
+        <v>46098</v>
+      </c>
+      <c r="J11" s="3">
+        <v>3</v>
+      </c>
+      <c r="K11" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="L11" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="M11" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="N11" s="3"/>
+      <c r="O11" s="3"/>
+      <c r="P11" s="3"/>
+      <c r="Q11" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="2"/>
+      <c r="B12" s="3">
+        <v>-5</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D12" s="3">
+        <v>26030964</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G12" s="4">
+        <v>46090</v>
+      </c>
+      <c r="H12" s="4">
+        <v>46091</v>
+      </c>
+      <c r="I12" s="4">
+        <v>46098</v>
+      </c>
+      <c r="J12" s="3">
+        <v>3</v>
+      </c>
+      <c r="K12" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="L12" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="M12" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="N12" s="3"/>
+      <c r="O12" s="3"/>
+      <c r="P12" s="3"/>
+      <c r="Q12" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="2"/>
+      <c r="B13" s="3">
+        <v>-5</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D13" s="3">
+        <v>26030964</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G13" s="4">
+        <v>46090</v>
+      </c>
+      <c r="H13" s="4">
+        <v>46091</v>
+      </c>
+      <c r="I13" s="4">
+        <v>46098</v>
+      </c>
+      <c r="J13" s="3">
+        <v>3</v>
+      </c>
+      <c r="K13" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="L13" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="M13" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="N13" s="3"/>
+      <c r="O13" s="3"/>
+      <c r="P13" s="3"/>
+      <c r="Q13" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="2"/>
+      <c r="B14" s="3">
+        <v>-5</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D14" s="3">
+        <v>26030964</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G14" s="4">
+        <v>46090</v>
+      </c>
+      <c r="H14" s="4">
+        <v>46091</v>
+      </c>
+      <c r="I14" s="4">
+        <v>46098</v>
+      </c>
+      <c r="J14" s="3">
+        <v>3</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="N14" s="3"/>
+      <c r="O14" s="3"/>
+      <c r="P14" s="3"/>
+      <c r="Q14" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="2"/>
+      <c r="B15" s="3">
+        <v>-5</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D15" s="3">
+        <v>26030964</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G15" s="4">
+        <v>46090</v>
+      </c>
+      <c r="H15" s="4">
+        <v>46091</v>
+      </c>
+      <c r="I15" s="4">
+        <v>46098</v>
+      </c>
+      <c r="J15" s="3">
+        <v>3</v>
+      </c>
+      <c r="K15" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="L15" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="M15" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="N15" s="3"/>
+      <c r="O15" s="3"/>
+      <c r="P15" s="3"/>
+      <c r="Q15" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="2"/>
+      <c r="B16" s="3">
+        <v>-5</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D16" s="3">
+        <v>26030964</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G16" s="4">
+        <v>46090</v>
+      </c>
+      <c r="H16" s="4">
+        <v>46091</v>
+      </c>
+      <c r="I16" s="4">
+        <v>46098</v>
+      </c>
+      <c r="J16" s="3">
+        <v>3</v>
+      </c>
+      <c r="K16" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="L16" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="M16" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="N16" s="3"/>
+      <c r="O16" s="3"/>
+      <c r="P16" s="3"/>
+      <c r="Q16" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="2"/>
+      <c r="B17" s="3">
+        <v>-5</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D17" s="3">
+        <v>26030964</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G17" s="4">
+        <v>46090</v>
+      </c>
+      <c r="H17" s="4">
+        <v>46091</v>
+      </c>
+      <c r="I17" s="4">
+        <v>46098</v>
+      </c>
+      <c r="J17" s="3">
+        <v>3</v>
+      </c>
+      <c r="K17" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="L17" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="M17" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="N17" s="3"/>
+      <c r="O17" s="3"/>
+      <c r="P17" s="3"/>
+      <c r="Q17" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="2"/>
+      <c r="B18" s="3">
+        <v>-5</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D18" s="3">
+        <v>26030964</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G18" s="4">
+        <v>46090</v>
+      </c>
+      <c r="H18" s="4">
+        <v>46091</v>
+      </c>
+      <c r="I18" s="4">
+        <v>46098</v>
+      </c>
+      <c r="J18" s="3">
+        <v>3</v>
+      </c>
+      <c r="K18" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="L18" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="M18" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="N18" s="3"/>
+      <c r="O18" s="3"/>
+      <c r="P18" s="3"/>
+      <c r="Q18" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="2"/>
+      <c r="B19" s="3">
+        <v>-5</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D19" s="3">
+        <v>26030964</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G19" s="4">
+        <v>46090</v>
+      </c>
+      <c r="H19" s="4">
+        <v>46091</v>
+      </c>
+      <c r="I19" s="4">
+        <v>46098</v>
+      </c>
+      <c r="J19" s="3">
+        <v>3</v>
+      </c>
+      <c r="K19" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="L19" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="M19" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="N19" s="3"/>
+      <c r="O19" s="3"/>
+      <c r="P19" s="3"/>
+      <c r="Q19" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="2"/>
+      <c r="B20" s="3">
+        <v>-5</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D20" s="3">
+        <v>26030964</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G20" s="4">
+        <v>46090</v>
+      </c>
+      <c r="H20" s="4">
+        <v>46091</v>
+      </c>
+      <c r="I20" s="4">
+        <v>46098</v>
+      </c>
+      <c r="J20" s="3">
+        <v>3</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="L20" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="M20" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="N20" s="3"/>
+      <c r="O20" s="3"/>
+      <c r="P20" s="3"/>
+      <c r="Q20" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="2"/>
+      <c r="B21" s="3">
+        <v>-5</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D21" s="3">
+        <v>26030964</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G21" s="4">
+        <v>46090</v>
+      </c>
+      <c r="H21" s="4">
+        <v>46091</v>
+      </c>
+      <c r="I21" s="4">
+        <v>46098</v>
+      </c>
+      <c r="J21" s="3">
+        <v>3</v>
+      </c>
+      <c r="K21" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="L21" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="M21" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="N21" s="3"/>
+      <c r="O21" s="3"/>
+      <c r="P21" s="3"/>
+      <c r="Q21" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="2"/>
+      <c r="B22" s="3">
+        <v>-5</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D22" s="3">
+        <v>26030964</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G22" s="4">
+        <v>46090</v>
+      </c>
+      <c r="H22" s="4">
+        <v>46091</v>
+      </c>
+      <c r="I22" s="4">
+        <v>46098</v>
+      </c>
+      <c r="J22" s="3">
+        <v>3</v>
+      </c>
+      <c r="K22" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="L22" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="M22" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="N22" s="3"/>
+      <c r="O22" s="3"/>
+      <c r="P22" s="3"/>
+      <c r="Q22" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="2"/>
+      <c r="B23" s="3">
+        <v>-5</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D23" s="3">
+        <v>26030964</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G23" s="4">
+        <v>46090</v>
+      </c>
+      <c r="H23" s="4">
+        <v>46091</v>
+      </c>
+      <c r="I23" s="4">
+        <v>46098</v>
+      </c>
+      <c r="J23" s="3">
+        <v>3</v>
+      </c>
+      <c r="K23" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="L23" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="M23" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="N23" s="3"/>
+      <c r="O23" s="3"/>
+      <c r="P23" s="3"/>
+      <c r="Q23" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="2"/>
+      <c r="B24" s="3">
+        <v>-5</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D24" s="3">
+        <v>26030964</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G24" s="4">
+        <v>46090</v>
+      </c>
+      <c r="H24" s="4">
+        <v>46091</v>
+      </c>
+      <c r="I24" s="4">
+        <v>46098</v>
+      </c>
+      <c r="J24" s="3">
+        <v>3</v>
+      </c>
+      <c r="K24" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="L24" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="M24" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="N24" s="3"/>
+      <c r="O24" s="3"/>
+      <c r="P24" s="3"/>
+      <c r="Q24" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="2"/>
+      <c r="B25" s="3">
+        <v>-5</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D25" s="3">
+        <v>26030964</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G25" s="4">
+        <v>46090</v>
+      </c>
+      <c r="H25" s="4">
+        <v>46091</v>
+      </c>
+      <c r="I25" s="4">
+        <v>46098</v>
+      </c>
+      <c r="J25" s="3">
+        <v>3</v>
+      </c>
+      <c r="K25" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="L25" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="M25" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="N25" s="3"/>
+      <c r="O25" s="3"/>
+      <c r="P25" s="3"/>
+      <c r="Q25" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="2"/>
+      <c r="B26" s="3">
+        <v>-5</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D26" s="3">
+        <v>26030964</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G26" s="4">
+        <v>46090</v>
+      </c>
+      <c r="H26" s="4">
+        <v>46091</v>
+      </c>
+      <c r="I26" s="4">
+        <v>46098</v>
+      </c>
+      <c r="J26" s="3">
+        <v>3</v>
+      </c>
+      <c r="K26" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="L26" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="M26" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="N26" s="3"/>
+      <c r="O26" s="3"/>
+      <c r="P26" s="3"/>
+      <c r="Q26" s="3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="2"/>
+      <c r="B27" s="3">
+        <v>-5</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D27" s="3">
+        <v>26030964</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G27" s="4">
+        <v>46090</v>
+      </c>
+      <c r="H27" s="4">
+        <v>46091</v>
+      </c>
+      <c r="I27" s="4">
+        <v>46098</v>
+      </c>
+      <c r="J27" s="3">
+        <v>3</v>
+      </c>
+      <c r="K27" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="L27" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="M27" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="N27" s="3"/>
+      <c r="O27" s="3"/>
+      <c r="P27" s="3"/>
+      <c r="Q27" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="2"/>
+      <c r="B28" s="3">
+        <v>-5</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D28" s="3">
+        <v>26030964</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G28" s="4">
+        <v>46090</v>
+      </c>
+      <c r="H28" s="4">
+        <v>46091</v>
+      </c>
+      <c r="I28" s="4">
+        <v>46098</v>
+      </c>
+      <c r="J28" s="3">
+        <v>3</v>
+      </c>
+      <c r="K28" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="L28" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="M28" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="N28" s="3"/>
+      <c r="O28" s="3"/>
+      <c r="P28" s="3"/>
+      <c r="Q28" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="2"/>
+      <c r="B29" s="3">
+        <v>-5</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D29" s="3">
+        <v>26030964</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G29" s="4">
+        <v>46090</v>
+      </c>
+      <c r="H29" s="4">
+        <v>46091</v>
+      </c>
+      <c r="I29" s="4">
+        <v>46098</v>
+      </c>
+      <c r="J29" s="3">
+        <v>3</v>
+      </c>
+      <c r="K29" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="L29" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="M29" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="N29" s="3"/>
+      <c r="O29" s="3"/>
+      <c r="P29" s="3"/>
+      <c r="Q29" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="2"/>
+      <c r="B30" s="3">
+        <v>0</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D30" s="3">
+        <v>26030966</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G30" s="4">
+        <v>46090</v>
+      </c>
+      <c r="H30" s="4">
+        <v>46091</v>
+      </c>
+      <c r="I30" s="4">
+        <v>46104</v>
+      </c>
+      <c r="J30" s="3">
+        <v>3</v>
+      </c>
+      <c r="K30" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="L30" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="M30" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="N30" s="3"/>
+      <c r="O30" s="3"/>
+      <c r="P30" s="3"/>
+      <c r="Q30" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="2"/>
+      <c r="B31" s="3">
+        <v>0</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D31" s="3">
+        <v>26030966</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G31" s="4">
+        <v>46090</v>
+      </c>
+      <c r="H31" s="4">
+        <v>46091</v>
+      </c>
+      <c r="I31" s="4">
+        <v>46104</v>
+      </c>
+      <c r="J31" s="3">
+        <v>3</v>
+      </c>
+      <c r="K31" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="L31" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="M31" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="N31" s="3"/>
+      <c r="O31" s="3"/>
+      <c r="P31" s="3"/>
+      <c r="Q31" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="2"/>
+      <c r="B32" s="3">
+        <v>0</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D32" s="3">
+        <v>26030966</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G32" s="4">
+        <v>46090</v>
+      </c>
+      <c r="H32" s="4">
+        <v>46091</v>
+      </c>
+      <c r="I32" s="4">
+        <v>46104</v>
+      </c>
+      <c r="J32" s="3">
+        <v>3</v>
+      </c>
+      <c r="K32" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="L32" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="M32" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="N32" s="3"/>
+      <c r="O32" s="3"/>
+      <c r="P32" s="3"/>
+      <c r="Q32" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="2"/>
+      <c r="B33" s="3">
+        <v>0</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D33" s="3">
+        <v>26030966</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G33" s="4">
+        <v>46090</v>
+      </c>
+      <c r="H33" s="4">
+        <v>46091</v>
+      </c>
+      <c r="I33" s="4">
+        <v>46104</v>
+      </c>
+      <c r="J33" s="3">
+        <v>3</v>
+      </c>
+      <c r="K33" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="L33" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="M33" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="N33" s="3"/>
+      <c r="O33" s="3"/>
+      <c r="P33" s="3"/>
+      <c r="Q33" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="2"/>
+      <c r="B34" s="3">
+        <v>0</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D34" s="3">
+        <v>26030966</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G34" s="4">
+        <v>46090</v>
+      </c>
+      <c r="H34" s="4">
+        <v>46091</v>
+      </c>
+      <c r="I34" s="4">
+        <v>46104</v>
+      </c>
+      <c r="J34" s="3">
+        <v>3</v>
+      </c>
+      <c r="K34" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="L34" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="M34" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="N34" s="3"/>
+      <c r="O34" s="3"/>
+      <c r="P34" s="3"/>
+      <c r="Q34" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="2"/>
+      <c r="B35" s="3">
+        <v>0</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D35" s="3">
+        <v>26030966</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G35" s="4">
+        <v>46090</v>
+      </c>
+      <c r="H35" s="4">
+        <v>46091</v>
+      </c>
+      <c r="I35" s="4">
+        <v>46104</v>
+      </c>
+      <c r="J35" s="3">
+        <v>3</v>
+      </c>
+      <c r="K35" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="L35" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="M35" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="N35" s="3"/>
+      <c r="O35" s="3"/>
+      <c r="P35" s="3"/>
+      <c r="Q35" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="2"/>
+      <c r="B36" s="3">
+        <v>0</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D36" s="3">
+        <v>26030966</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G36" s="4">
+        <v>46090</v>
+      </c>
+      <c r="H36" s="4">
+        <v>46091</v>
+      </c>
+      <c r="I36" s="4">
+        <v>46104</v>
+      </c>
+      <c r="J36" s="3">
+        <v>3</v>
+      </c>
+      <c r="K36" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="L36" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="M36" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="N36" s="3"/>
+      <c r="O36" s="3"/>
+      <c r="P36" s="3"/>
+      <c r="Q36" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="2"/>
+      <c r="B37" s="3">
+        <v>0</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D37" s="3">
+        <v>26030966</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G37" s="4">
+        <v>46090</v>
+      </c>
+      <c r="H37" s="4">
+        <v>46091</v>
+      </c>
+      <c r="I37" s="4">
+        <v>46104</v>
+      </c>
+      <c r="J37" s="3">
+        <v>3</v>
+      </c>
+      <c r="K37" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="L37" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="M37" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="N37" s="3"/>
+      <c r="O37" s="3"/>
+      <c r="P37" s="3"/>
+      <c r="Q37" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="2"/>
+      <c r="B38" s="3">
+        <v>0</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D38" s="3">
+        <v>26030966</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G38" s="4">
+        <v>46090</v>
+      </c>
+      <c r="H38" s="4">
+        <v>46091</v>
+      </c>
+      <c r="I38" s="4">
+        <v>46104</v>
+      </c>
+      <c r="J38" s="3">
+        <v>3</v>
+      </c>
+      <c r="K38" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="L38" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="M38" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="N38" s="3"/>
+      <c r="O38" s="3"/>
+      <c r="P38" s="3"/>
+      <c r="Q38" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="2"/>
+      <c r="B39" s="3">
+        <v>0</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D39" s="3">
+        <v>26030966</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F39" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G39" s="4">
+        <v>46090</v>
+      </c>
+      <c r="H39" s="4">
+        <v>46091</v>
+      </c>
+      <c r="I39" s="4">
+        <v>46104</v>
+      </c>
+      <c r="J39" s="3">
+        <v>3</v>
+      </c>
+      <c r="K39" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="L39" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="M39" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="N39" s="3"/>
+      <c r="O39" s="3"/>
+      <c r="P39" s="3"/>
+      <c r="Q39" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="2"/>
+      <c r="B40" s="3">
+        <v>0</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D40" s="3">
+        <v>26030966</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="F40" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G40" s="4">
+        <v>46090</v>
+      </c>
+      <c r="H40" s="4">
+        <v>46091</v>
+      </c>
+      <c r="I40" s="4">
+        <v>46104</v>
+      </c>
+      <c r="J40" s="3">
+        <v>3</v>
+      </c>
+      <c r="K40" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="L40" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="M40" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="N40" s="3"/>
+      <c r="O40" s="3"/>
+      <c r="P40" s="3"/>
+      <c r="Q40" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="2"/>
+      <c r="B41" s="3">
+        <v>0</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D41" s="3">
+        <v>26030966</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G41" s="4">
+        <v>46090</v>
+      </c>
+      <c r="H41" s="4">
+        <v>46091</v>
+      </c>
+      <c r="I41" s="4">
+        <v>46104</v>
+      </c>
+      <c r="J41" s="3">
+        <v>3</v>
+      </c>
+      <c r="K41" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="L41" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="M41" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="N41" s="3"/>
+      <c r="O41" s="3"/>
+      <c r="P41" s="3"/>
+      <c r="Q41" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="2"/>
+      <c r="B42" s="3">
+        <v>0</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D42" s="3">
+        <v>26030966</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G42" s="4">
+        <v>46090</v>
+      </c>
+      <c r="H42" s="4">
+        <v>46091</v>
+      </c>
+      <c r="I42" s="4">
+        <v>46104</v>
+      </c>
+      <c r="J42" s="3">
+        <v>3</v>
+      </c>
+      <c r="K42" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="L42" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="M42" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="N42" s="3"/>
+      <c r="O42" s="3"/>
+      <c r="P42" s="3"/>
+      <c r="Q42" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="2"/>
+      <c r="B43" s="3">
+        <v>0</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D43" s="3">
+        <v>26030966</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G43" s="4">
+        <v>46090</v>
+      </c>
+      <c r="H43" s="4">
+        <v>46091</v>
+      </c>
+      <c r="I43" s="4">
+        <v>46104</v>
+      </c>
+      <c r="J43" s="3">
+        <v>3</v>
+      </c>
+      <c r="K43" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="L43" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="M43" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="N43" s="3"/>
+      <c r="O43" s="3"/>
+      <c r="P43" s="3"/>
+      <c r="Q43" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="2"/>
+      <c r="B44" s="3">
+        <v>0</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D44" s="3">
+        <v>26030966</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G44" s="4">
+        <v>46090</v>
+      </c>
+      <c r="H44" s="4">
+        <v>46091</v>
+      </c>
+      <c r="I44" s="4">
+        <v>46104</v>
+      </c>
+      <c r="J44" s="3">
+        <v>3</v>
+      </c>
+      <c r="K44" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="L44" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="M44" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="N44" s="3"/>
+      <c r="O44" s="3"/>
+      <c r="P44" s="3"/>
+      <c r="Q44" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="2"/>
+      <c r="B45" s="3">
+        <v>0</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D45" s="3">
+        <v>26030966</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G45" s="4">
+        <v>46090</v>
+      </c>
+      <c r="H45" s="4">
+        <v>46091</v>
+      </c>
+      <c r="I45" s="4">
+        <v>46104</v>
+      </c>
+      <c r="J45" s="3">
+        <v>3</v>
+      </c>
+      <c r="K45" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="L45" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="M45" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="N45" s="3"/>
+      <c r="O45" s="3"/>
+      <c r="P45" s="3"/>
+      <c r="Q45" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="2"/>
+      <c r="B46" s="3">
+        <v>0</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D46" s="3">
+        <v>26030966</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="F46" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G46" s="4">
+        <v>46090</v>
+      </c>
+      <c r="H46" s="4">
+        <v>46091</v>
+      </c>
+      <c r="I46" s="4">
+        <v>46104</v>
+      </c>
+      <c r="J46" s="3">
+        <v>3</v>
+      </c>
+      <c r="K46" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="L46" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="M46" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="N46" s="3"/>
+      <c r="O46" s="3"/>
+      <c r="P46" s="3"/>
+      <c r="Q46" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="2"/>
+      <c r="B47" s="3">
+        <v>0</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D47" s="3">
+        <v>26030966</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G47" s="4">
+        <v>46090</v>
+      </c>
+      <c r="H47" s="4">
+        <v>46091</v>
+      </c>
+      <c r="I47" s="4">
+        <v>46104</v>
+      </c>
+      <c r="J47" s="3">
+        <v>3</v>
+      </c>
+      <c r="K47" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="L47" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="M47" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="N47" s="3"/>
+      <c r="O47" s="3"/>
+      <c r="P47" s="3"/>
+      <c r="Q47" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="2"/>
+      <c r="B48" s="3">
+        <v>4</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D48" s="3">
+        <v>26031383</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G48" s="4">
+        <v>46094</v>
+      </c>
+      <c r="H48" s="4">
+        <v>46094</v>
+      </c>
+      <c r="I48" s="4">
+        <v>46108</v>
+      </c>
+      <c r="J48" s="3">
+        <v>3</v>
+      </c>
+      <c r="K48" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="L48" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="M48" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="N48" s="3"/>
+      <c r="O48" s="3"/>
+      <c r="P48" s="3"/>
+      <c r="Q48" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="2"/>
+      <c r="B49" s="3">
+        <v>4</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D49" s="3">
+        <v>26031383</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F49" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G49" s="4">
+        <v>46094</v>
+      </c>
+      <c r="H49" s="4">
+        <v>46094</v>
+      </c>
+      <c r="I49" s="4">
+        <v>46108</v>
+      </c>
+      <c r="J49" s="3">
+        <v>3</v>
+      </c>
+      <c r="K49" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="L49" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="M49" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="N49" s="3"/>
+      <c r="O49" s="3"/>
+      <c r="P49" s="3"/>
+      <c r="Q49" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="2"/>
+      <c r="B50" s="3">
+        <v>4</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D50" s="3">
+        <v>26031383</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F50" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G50" s="4">
+        <v>46094</v>
+      </c>
+      <c r="H50" s="4">
+        <v>46094</v>
+      </c>
+      <c r="I50" s="4">
+        <v>46108</v>
+      </c>
+      <c r="J50" s="3">
+        <v>3</v>
+      </c>
+      <c r="K50" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="L50" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="M50" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="N50" s="3"/>
+      <c r="O50" s="3"/>
+      <c r="P50" s="3"/>
+      <c r="Q50" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="2"/>
+      <c r="B51" s="3">
+        <v>4</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D51" s="3">
+        <v>26031383</v>
+      </c>
+      <c r="E51" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F51" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G51" s="4">
+        <v>46094</v>
+      </c>
+      <c r="H51" s="4">
+        <v>46094</v>
+      </c>
+      <c r="I51" s="4">
+        <v>46108</v>
+      </c>
+      <c r="J51" s="3">
+        <v>3</v>
+      </c>
+      <c r="K51" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="L51" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="M51" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="N51" s="3"/>
+      <c r="O51" s="3"/>
+      <c r="P51" s="3"/>
+      <c r="Q51" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="2"/>
+      <c r="B52" s="3">
+        <v>4</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D52" s="3">
+        <v>26031383</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G52" s="4">
+        <v>46094</v>
+      </c>
+      <c r="H52" s="4">
+        <v>46094</v>
+      </c>
+      <c r="I52" s="4">
+        <v>46108</v>
+      </c>
+      <c r="J52" s="3">
+        <v>3</v>
+      </c>
+      <c r="K52" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="L52" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="M52" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="N52" s="3"/>
+      <c r="O52" s="3"/>
+      <c r="P52" s="3"/>
+      <c r="Q52" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="2"/>
+      <c r="B53" s="3">
+        <v>4</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D53" s="3">
+        <v>26031383</v>
+      </c>
+      <c r="E53" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F53" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G53" s="4">
+        <v>46094</v>
+      </c>
+      <c r="H53" s="4">
+        <v>46094</v>
+      </c>
+      <c r="I53" s="4">
+        <v>46108</v>
+      </c>
+      <c r="J53" s="3">
+        <v>3</v>
+      </c>
+      <c r="K53" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="L53" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="M53" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="N53" s="3"/>
+      <c r="O53" s="3"/>
+      <c r="P53" s="3"/>
+      <c r="Q53" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="2"/>
+      <c r="B54" s="3">
+        <v>4</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D54" s="3">
+        <v>26031383</v>
+      </c>
+      <c r="E54" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F54" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G54" s="4">
+        <v>46094</v>
+      </c>
+      <c r="H54" s="4">
+        <v>46094</v>
+      </c>
+      <c r="I54" s="4">
+        <v>46108</v>
+      </c>
+      <c r="J54" s="3">
+        <v>3</v>
+      </c>
+      <c r="K54" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="L54" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="M54" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="N54" s="3"/>
+      <c r="O54" s="3"/>
+      <c r="P54" s="3"/>
+      <c r="Q54" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="2"/>
+      <c r="B55" s="3">
+        <v>4</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D55" s="3">
+        <v>26031383</v>
+      </c>
+      <c r="E55" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F55" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G55" s="4">
+        <v>46094</v>
+      </c>
+      <c r="H55" s="4">
+        <v>46094</v>
+      </c>
+      <c r="I55" s="4">
+        <v>46108</v>
+      </c>
+      <c r="J55" s="3">
+        <v>3</v>
+      </c>
+      <c r="K55" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="L55" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="M55" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="N55" s="3"/>
+      <c r="O55" s="3"/>
+      <c r="P55" s="3"/>
+      <c r="Q55" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="2"/>
+      <c r="B56" s="3">
+        <v>4</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D56" s="3">
+        <v>26031383</v>
+      </c>
+      <c r="E56" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F56" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G56" s="4">
+        <v>46094</v>
+      </c>
+      <c r="H56" s="4">
+        <v>46094</v>
+      </c>
+      <c r="I56" s="4">
+        <v>46108</v>
+      </c>
+      <c r="J56" s="3">
+        <v>3</v>
+      </c>
+      <c r="K56" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="L56" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="M56" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="N56" s="3"/>
+      <c r="O56" s="3"/>
+      <c r="P56" s="3"/>
+      <c r="Q56" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="2"/>
+      <c r="B57" s="3">
+        <v>4</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D57" s="3">
+        <v>26031383</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F57" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G57" s="4">
+        <v>46094</v>
+      </c>
+      <c r="H57" s="4">
+        <v>46094</v>
+      </c>
+      <c r="I57" s="4">
+        <v>46108</v>
+      </c>
+      <c r="J57" s="3">
+        <v>3</v>
+      </c>
+      <c r="K57" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="L57" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="M57" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="N57" s="3"/>
+      <c r="O57" s="3"/>
+      <c r="P57" s="3"/>
+      <c r="Q57" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="2"/>
+      <c r="B58" s="3">
+        <v>4</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D58" s="3">
+        <v>26031383</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F58" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G58" s="4">
+        <v>46094</v>
+      </c>
+      <c r="H58" s="4">
+        <v>46094</v>
+      </c>
+      <c r="I58" s="4">
+        <v>46108</v>
+      </c>
+      <c r="J58" s="3">
+        <v>3</v>
+      </c>
+      <c r="K58" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="L58" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="M58" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="N58" s="3"/>
+      <c r="O58" s="3"/>
+      <c r="P58" s="3"/>
+      <c r="Q58" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="2"/>
+      <c r="B59" s="3">
+        <v>4</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D59" s="3">
+        <v>26032281</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G59" s="4">
+        <v>46100</v>
+      </c>
+      <c r="H59" s="4">
+        <v>46100</v>
+      </c>
+      <c r="I59" s="4">
+        <v>46108</v>
+      </c>
+      <c r="J59" s="3">
+        <v>3</v>
+      </c>
+      <c r="K59" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="L59" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="M59" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="N59" s="3"/>
+      <c r="O59" s="3"/>
+      <c r="P59" s="3"/>
+      <c r="Q59" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="2"/>
+      <c r="B60" s="3">
+        <v>4</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D60" s="3">
+        <v>26032281</v>
+      </c>
+      <c r="E60" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F60" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G60" s="4">
+        <v>46100</v>
+      </c>
+      <c r="H60" s="4">
+        <v>46100</v>
+      </c>
+      <c r="I60" s="4">
+        <v>46108</v>
+      </c>
+      <c r="J60" s="3">
+        <v>3</v>
+      </c>
+      <c r="K60" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="L60" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="M60" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="N60" s="3"/>
+      <c r="O60" s="3"/>
+      <c r="P60" s="3"/>
+      <c r="Q60" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="2"/>
+      <c r="B61" s="3">
+        <v>4</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D61" s="3">
+        <v>26032281</v>
+      </c>
+      <c r="E61" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F61" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G61" s="4">
+        <v>46100</v>
+      </c>
+      <c r="H61" s="4">
+        <v>46100</v>
+      </c>
+      <c r="I61" s="4">
+        <v>46108</v>
+      </c>
+      <c r="J61" s="3">
+        <v>3</v>
+      </c>
+      <c r="K61" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="L61" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="M61" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="N61" s="3"/>
+      <c r="O61" s="3"/>
+      <c r="P61" s="3"/>
+      <c r="Q61" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="2"/>
+      <c r="B62" s="3">
+        <v>4</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D62" s="3">
+        <v>26032281</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G62" s="4">
+        <v>46100</v>
+      </c>
+      <c r="H62" s="4">
+        <v>46100</v>
+      </c>
+      <c r="I62" s="4">
+        <v>46108</v>
+      </c>
+      <c r="J62" s="3">
+        <v>3</v>
+      </c>
+      <c r="K62" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="L62" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="M62" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="N62" s="3"/>
+      <c r="O62" s="3"/>
+      <c r="P62" s="3"/>
+      <c r="Q62" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="2"/>
+      <c r="B63" s="3">
+        <v>7</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D63" s="3">
+        <v>26032652</v>
+      </c>
+      <c r="E63" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F63" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G63" s="4">
+        <v>46101</v>
+      </c>
+      <c r="H63" s="4">
+        <v>46101</v>
+      </c>
+      <c r="I63" s="4">
+        <v>46111</v>
+      </c>
+      <c r="J63" s="3">
+        <v>3</v>
+      </c>
+      <c r="K63" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="L63" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="M63" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="N63" s="3"/>
+      <c r="O63" s="3"/>
+      <c r="P63" s="3"/>
+      <c r="Q63" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="2"/>
+      <c r="B64" s="3">
+        <v>7</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D64" s="3">
+        <v>26032652</v>
+      </c>
+      <c r="E64" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F64" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G64" s="4">
+        <v>46101</v>
+      </c>
+      <c r="H64" s="4">
+        <v>46101</v>
+      </c>
+      <c r="I64" s="4">
+        <v>46111</v>
+      </c>
+      <c r="J64" s="3">
+        <v>3</v>
+      </c>
+      <c r="K64" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="L64" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="M64" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="N64" s="3"/>
+      <c r="O64" s="3"/>
+      <c r="P64" s="3"/>
+      <c r="Q64" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="2"/>
+      <c r="B65" s="3">
+        <v>7</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D65" s="3">
+        <v>26032652</v>
+      </c>
+      <c r="E65" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F65" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G65" s="4">
+        <v>46101</v>
+      </c>
+      <c r="H65" s="4">
+        <v>46101</v>
+      </c>
+      <c r="I65" s="4">
+        <v>46111</v>
+      </c>
+      <c r="J65" s="3">
+        <v>3</v>
+      </c>
+      <c r="K65" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="L65" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="M65" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="N65" s="3"/>
+      <c r="O65" s="3"/>
+      <c r="P65" s="3"/>
+      <c r="Q65" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="2"/>
+      <c r="B66" s="3">
+        <v>7</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D66" s="3">
+        <v>26032652</v>
+      </c>
+      <c r="E66" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F66" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G66" s="4">
+        <v>46101</v>
+      </c>
+      <c r="H66" s="4">
+        <v>46101</v>
+      </c>
+      <c r="I66" s="4">
+        <v>46111</v>
+      </c>
+      <c r="J66" s="3">
+        <v>3</v>
+      </c>
+      <c r="K66" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="L66" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="M66" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="N66" s="3"/>
+      <c r="O66" s="3"/>
+      <c r="P66" s="3"/>
+      <c r="Q66" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="2"/>
+      <c r="B67" s="3">
+        <v>7</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D67" s="3">
+        <v>26032652</v>
+      </c>
+      <c r="E67" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F67" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G67" s="4">
+        <v>46101</v>
+      </c>
+      <c r="H67" s="4">
+        <v>46101</v>
+      </c>
+      <c r="I67" s="4">
+        <v>46111</v>
+      </c>
+      <c r="J67" s="3">
+        <v>3</v>
+      </c>
+      <c r="K67" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="L67" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="M67" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="N67" s="3"/>
+      <c r="O67" s="3"/>
+      <c r="P67" s="3"/>
+      <c r="Q67" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="2"/>
+      <c r="B68" s="3">
+        <v>7</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D68" s="3">
+        <v>26032652</v>
+      </c>
+      <c r="E68" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F68" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G68" s="4">
+        <v>46101</v>
+      </c>
+      <c r="H68" s="4">
+        <v>46101</v>
+      </c>
+      <c r="I68" s="4">
+        <v>46111</v>
+      </c>
+      <c r="J68" s="3">
+        <v>3</v>
+      </c>
+      <c r="K68" s="3"/>
+      <c r="L68" s="3"/>
+      <c r="M68" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="N68" s="3"/>
+      <c r="O68" s="3"/>
+      <c r="P68" s="3"/>
+      <c r="Q68" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="2"/>
+      <c r="B69" s="3">
+        <v>7</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D69" s="3">
+        <v>26032652</v>
+      </c>
+      <c r="E69" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F69" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G69" s="4">
+        <v>46101</v>
+      </c>
+      <c r="H69" s="4">
+        <v>46101</v>
+      </c>
+      <c r="I69" s="4">
+        <v>46111</v>
+      </c>
+      <c r="J69" s="3">
+        <v>3</v>
+      </c>
+      <c r="K69" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="L69" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="M69" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="N69" s="3"/>
+      <c r="O69" s="3"/>
+      <c r="P69" s="3"/>
+      <c r="Q69" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A70" s="2"/>
+      <c r="B70" s="3">
+        <v>7</v>
+      </c>
+      <c r="C70" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D70" s="3">
+        <v>26032652</v>
+      </c>
+      <c r="E70" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F70" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G70" s="4">
+        <v>46101</v>
+      </c>
+      <c r="H70" s="4">
+        <v>46101</v>
+      </c>
+      <c r="I70" s="4">
+        <v>46111</v>
+      </c>
+      <c r="J70" s="3">
+        <v>3</v>
+      </c>
+      <c r="K70" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="L70" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="M70" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="N70" s="3"/>
+      <c r="O70" s="3"/>
+      <c r="P70" s="3"/>
+      <c r="Q70" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A71" s="2"/>
+      <c r="B71" s="3">
+        <v>7</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D71" s="3">
+        <v>26032652</v>
+      </c>
+      <c r="E71" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F71" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G71" s="4">
+        <v>46101</v>
+      </c>
+      <c r="H71" s="4">
+        <v>46101</v>
+      </c>
+      <c r="I71" s="4">
+        <v>46111</v>
+      </c>
+      <c r="J71" s="3">
+        <v>3</v>
+      </c>
+      <c r="K71" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="L71" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="M71" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="N71" s="3"/>
+      <c r="O71" s="3"/>
+      <c r="P71" s="3"/>
+      <c r="Q71" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A72" s="2"/>
+      <c r="B72" s="3">
+        <v>7</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D72" s="3">
+        <v>26032652</v>
+      </c>
+      <c r="E72" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F72" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G72" s="4">
+        <v>46101</v>
+      </c>
+      <c r="H72" s="4">
+        <v>46101</v>
+      </c>
+      <c r="I72" s="4">
+        <v>46111</v>
+      </c>
+      <c r="J72" s="3">
+        <v>3</v>
+      </c>
+      <c r="K72" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="L72" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="M72" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="N72" s="3"/>
+      <c r="O72" s="3"/>
+      <c r="P72" s="3"/>
+      <c r="Q72" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A73" s="2"/>
+      <c r="B73" s="3">
+        <v>7</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D73" s="3">
+        <v>26032652</v>
+      </c>
+      <c r="E73" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F73" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G73" s="4">
+        <v>46101</v>
+      </c>
+      <c r="H73" s="4">
+        <v>46101</v>
+      </c>
+      <c r="I73" s="4">
+        <v>46111</v>
+      </c>
+      <c r="J73" s="3">
+        <v>3</v>
+      </c>
+      <c r="K73" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="L73" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="M73" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="N73" s="3"/>
+      <c r="O73" s="3"/>
+      <c r="P73" s="3"/>
+      <c r="Q73" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="2"/>
+      <c r="B74" s="3">
+        <v>7</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D74" s="3">
+        <v>26032652</v>
+      </c>
+      <c r="E74" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="F74" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G74" s="4">
+        <v>46101</v>
+      </c>
+      <c r="H74" s="4">
+        <v>46101</v>
+      </c>
+      <c r="I74" s="4">
+        <v>46111</v>
+      </c>
+      <c r="J74" s="3">
+        <v>3</v>
+      </c>
+      <c r="K74" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="L74" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="M74" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="N74" s="3"/>
+      <c r="O74" s="3"/>
+      <c r="P74" s="3"/>
+      <c r="Q74" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A75" s="2"/>
+      <c r="B75" s="3">
+        <v>7</v>
+      </c>
+      <c r="C75" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D75" s="3">
+        <v>26032652</v>
+      </c>
+      <c r="E75" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F75" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G75" s="4">
+        <v>46101</v>
+      </c>
+      <c r="H75" s="4">
+        <v>46101</v>
+      </c>
+      <c r="I75" s="4">
+        <v>46111</v>
+      </c>
+      <c r="J75" s="3">
+        <v>3</v>
+      </c>
+      <c r="K75" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="L75" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="M75" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="N75" s="3"/>
+      <c r="O75" s="3"/>
+      <c r="P75" s="3"/>
+      <c r="Q75" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A76" s="2"/>
+      <c r="B76" s="3">
+        <v>8</v>
+      </c>
+      <c r="C76" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D76" s="3">
+        <v>26031972</v>
+      </c>
+      <c r="E76" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F76" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="G76" s="4">
+        <v>46098</v>
+      </c>
+      <c r="H76" s="4">
+        <v>46099</v>
+      </c>
+      <c r="I76" s="4">
+        <v>46112</v>
+      </c>
+      <c r="J76" s="3">
+        <v>3</v>
+      </c>
+      <c r="K76" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="L76" s="3">
+        <v>1422</v>
+      </c>
+      <c r="M76" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="N76" s="3"/>
+      <c r="O76" s="3"/>
+      <c r="P76" s="3"/>
+      <c r="Q76" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A77" s="2"/>
+      <c r="B77" s="3">
+        <v>8</v>
+      </c>
+      <c r="C77" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D77" s="3">
+        <v>26031972</v>
+      </c>
+      <c r="E77" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F77" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="G77" s="4">
+        <v>46098</v>
+      </c>
+      <c r="H77" s="4">
+        <v>46099</v>
+      </c>
+      <c r="I77" s="4">
+        <v>46112</v>
+      </c>
+      <c r="J77" s="3">
+        <v>3</v>
+      </c>
+      <c r="K77" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="L77" s="3">
+        <v>1475</v>
+      </c>
+      <c r="M77" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="N77" s="3"/>
+      <c r="O77" s="3"/>
+      <c r="P77" s="3"/>
+      <c r="Q77" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A78" s="2"/>
+      <c r="B78" s="3">
+        <v>8</v>
+      </c>
+      <c r="C78" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D78" s="3">
+        <v>26031972</v>
+      </c>
+      <c r="E78" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F78" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="G78" s="4">
+        <v>46098</v>
+      </c>
+      <c r="H78" s="4">
+        <v>46099</v>
+      </c>
+      <c r="I78" s="4">
+        <v>46112</v>
+      </c>
+      <c r="J78" s="3">
+        <v>3</v>
+      </c>
+      <c r="K78" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="L78" s="3">
+        <v>4755</v>
+      </c>
+      <c r="M78" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="N78" s="3"/>
+      <c r="O78" s="3"/>
+      <c r="P78" s="3"/>
+      <c r="Q78" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A79" s="2"/>
+      <c r="B79" s="3">
+        <v>8</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D79" s="3">
+        <v>26031972</v>
+      </c>
+      <c r="E79" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F79" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="G79" s="4">
+        <v>46098</v>
+      </c>
+      <c r="H79" s="4">
+        <v>46099</v>
+      </c>
+      <c r="I79" s="4">
+        <v>46112</v>
+      </c>
+      <c r="J79" s="3">
+        <v>3</v>
+      </c>
+      <c r="K79" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="L79" s="3">
+        <v>1301</v>
+      </c>
+      <c r="M79" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="N79" s="3"/>
+      <c r="O79" s="3"/>
+      <c r="P79" s="3"/>
+      <c r="Q79" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A80" s="2"/>
+      <c r="B80" s="3">
+        <v>8</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D80" s="3">
+        <v>26031972</v>
+      </c>
+      <c r="E80" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F80" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="G80" s="4">
+        <v>46098</v>
+      </c>
+      <c r="H80" s="4">
+        <v>46099</v>
+      </c>
+      <c r="I80" s="4">
+        <v>46112</v>
+      </c>
+      <c r="J80" s="3">
+        <v>3</v>
+      </c>
+      <c r="K80" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="L80" s="3">
+        <v>1104</v>
+      </c>
+      <c r="M80" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="N80" s="3"/>
+      <c r="O80" s="3"/>
+      <c r="P80" s="3"/>
+      <c r="Q80" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A81" s="2"/>
+      <c r="B81" s="3">
+        <v>8</v>
+      </c>
+      <c r="C81" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D81" s="3">
+        <v>26031972</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F81" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="G81" s="4">
+        <v>46098</v>
+      </c>
+      <c r="H81" s="4">
+        <v>46099</v>
+      </c>
+      <c r="I81" s="4">
+        <v>46112</v>
+      </c>
+      <c r="J81" s="3">
+        <v>3</v>
+      </c>
+      <c r="K81" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="L81" s="3">
+        <v>1292</v>
+      </c>
+      <c r="M81" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="N81" s="3"/>
+      <c r="O81" s="3"/>
+      <c r="P81" s="3"/>
+      <c r="Q81" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A82" s="2"/>
+      <c r="B82" s="3">
+        <v>8</v>
+      </c>
+      <c r="C82" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D82" s="3">
+        <v>26031972</v>
+      </c>
+      <c r="E82" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F82" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="G82" s="4">
+        <v>46098</v>
+      </c>
+      <c r="H82" s="4">
+        <v>46099</v>
+      </c>
+      <c r="I82" s="4">
+        <v>46112</v>
+      </c>
+      <c r="J82" s="3">
+        <v>3</v>
+      </c>
+      <c r="K82" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="L82" s="3">
+        <v>1342</v>
+      </c>
+      <c r="M82" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="N82" s="3"/>
+      <c r="O82" s="3"/>
+      <c r="P82" s="3"/>
+      <c r="Q82" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A83" s="2"/>
+      <c r="B83" s="3">
+        <v>8</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D83" s="3">
+        <v>26031972</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="G83" s="4">
+        <v>46098</v>
+      </c>
+      <c r="H83" s="4">
+        <v>46099</v>
+      </c>
+      <c r="I83" s="4">
+        <v>46112</v>
+      </c>
+      <c r="J83" s="3">
+        <v>3</v>
+      </c>
+      <c r="K83" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="L83" s="3">
+        <v>4265</v>
+      </c>
+      <c r="M83" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="N83" s="3"/>
+      <c r="O83" s="3"/>
+      <c r="P83" s="3"/>
+      <c r="Q83" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A84" s="2"/>
+      <c r="B84" s="3">
+        <v>8</v>
+      </c>
+      <c r="C84" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D84" s="3">
+        <v>26031972</v>
+      </c>
+      <c r="E84" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F84" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="G84" s="4">
+        <v>46098</v>
+      </c>
+      <c r="H84" s="4">
+        <v>46099</v>
+      </c>
+      <c r="I84" s="4">
+        <v>46112</v>
+      </c>
+      <c r="J84" s="3">
+        <v>3</v>
+      </c>
+      <c r="K84" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="L84" s="3">
+        <v>4000</v>
+      </c>
+      <c r="M84" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="N84" s="3"/>
+      <c r="O84" s="3"/>
+      <c r="P84" s="3"/>
+      <c r="Q84" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A85" s="2"/>
+      <c r="B85" s="3">
+        <v>8</v>
+      </c>
+      <c r="C85" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D85" s="3">
+        <v>26031972</v>
+      </c>
+      <c r="E85" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F85" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="G85" s="4">
+        <v>46098</v>
+      </c>
+      <c r="H85" s="4">
+        <v>46099</v>
+      </c>
+      <c r="I85" s="4">
+        <v>46112</v>
+      </c>
+      <c r="J85" s="3">
+        <v>3</v>
+      </c>
+      <c r="K85" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="L85" s="3">
+        <v>1276</v>
+      </c>
+      <c r="M85" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="N85" s="3"/>
+      <c r="O85" s="3"/>
+      <c r="P85" s="3"/>
+      <c r="Q85" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A86" s="2"/>
+      <c r="B86" s="3">
+        <v>8</v>
+      </c>
+      <c r="C86" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D86" s="3">
+        <v>26031972</v>
+      </c>
+      <c r="E86" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F86" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="G86" s="4">
+        <v>46098</v>
+      </c>
+      <c r="H86" s="4">
+        <v>46099</v>
+      </c>
+      <c r="I86" s="4">
+        <v>46112</v>
+      </c>
+      <c r="J86" s="3">
+        <v>3</v>
+      </c>
+      <c r="K86" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="L86" s="3">
+        <v>1052</v>
+      </c>
+      <c r="M86" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="N86" s="3"/>
+      <c r="O86" s="3"/>
+      <c r="P86" s="3"/>
+      <c r="Q86" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A87" s="2"/>
+      <c r="B87" s="3">
+        <v>8</v>
+      </c>
+      <c r="C87" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D87" s="3">
+        <v>26031972</v>
+      </c>
+      <c r="E87" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="F87" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="G87" s="4">
+        <v>46098</v>
+      </c>
+      <c r="H87" s="4">
+        <v>46099</v>
+      </c>
+      <c r="I87" s="4">
+        <v>46112</v>
+      </c>
+      <c r="J87" s="3">
+        <v>3</v>
+      </c>
+      <c r="K87" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="L87" s="3">
+        <v>1265</v>
+      </c>
+      <c r="M87" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="N87" s="3"/>
+      <c r="O87" s="3"/>
+      <c r="P87" s="3"/>
+      <c r="Q87" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A88" s="2"/>
+      <c r="B88" s="3">
+        <v>8</v>
+      </c>
+      <c r="C88" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D88" s="3">
+        <v>26031972</v>
+      </c>
+      <c r="E88" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F88" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="G88" s="4">
+        <v>46098</v>
+      </c>
+      <c r="H88" s="4">
+        <v>46099</v>
+      </c>
+      <c r="I88" s="4">
+        <v>46112</v>
+      </c>
+      <c r="J88" s="3">
+        <v>3</v>
+      </c>
+      <c r="K88" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="L88" s="3">
+        <v>1424</v>
+      </c>
+      <c r="M88" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="N88" s="3"/>
+      <c r="O88" s="3"/>
+      <c r="P88" s="3"/>
+      <c r="Q88" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A89" s="2"/>
+      <c r="B89" s="3">
+        <v>8</v>
+      </c>
+      <c r="C89" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D89" s="3">
+        <v>26031972</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="F89" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="G89" s="4">
+        <v>46098</v>
+      </c>
+      <c r="H89" s="4">
+        <v>46099</v>
+      </c>
+      <c r="I89" s="4">
+        <v>46112</v>
+      </c>
+      <c r="J89" s="3">
+        <v>3</v>
+      </c>
+      <c r="K89" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="L89" s="3">
+        <v>1108</v>
+      </c>
+      <c r="M89" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="N89" s="3"/>
+      <c r="O89" s="3"/>
+      <c r="P89" s="3"/>
+      <c r="Q89" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A90" s="2"/>
+      <c r="B90" s="3">
+        <v>8</v>
+      </c>
+      <c r="C90" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D90" s="3">
+        <v>26031972</v>
+      </c>
+      <c r="E90" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="F90" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="G90" s="4">
+        <v>46098</v>
+      </c>
+      <c r="H90" s="4">
+        <v>46099</v>
+      </c>
+      <c r="I90" s="4">
+        <v>46112</v>
+      </c>
+      <c r="J90" s="3">
+        <v>3</v>
+      </c>
+      <c r="K90" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="L90" s="3">
+        <v>1263</v>
+      </c>
+      <c r="M90" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="N90" s="3"/>
+      <c r="O90" s="3"/>
+      <c r="P90" s="3"/>
+      <c r="Q90" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A91" s="2"/>
+      <c r="B91" s="3">
+        <v>8</v>
+      </c>
+      <c r="C91" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D91" s="3">
+        <v>26031972</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="G91" s="4">
+        <v>46098</v>
+      </c>
+      <c r="H91" s="4">
+        <v>46099</v>
+      </c>
+      <c r="I91" s="4">
+        <v>46112</v>
+      </c>
+      <c r="J91" s="3">
+        <v>3</v>
+      </c>
+      <c r="K91" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="L91" s="3">
+        <v>4002</v>
+      </c>
+      <c r="M91" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="N91" s="3"/>
+      <c r="O91" s="3"/>
+      <c r="P91" s="3"/>
+      <c r="Q91" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A92" s="2"/>
+      <c r="B92" s="3">
+        <v>8</v>
+      </c>
+      <c r="C92" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D92" s="3">
+        <v>26031972</v>
+      </c>
+      <c r="E92" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F92" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="G92" s="4">
+        <v>46098</v>
+      </c>
+      <c r="H92" s="4">
+        <v>46099</v>
+      </c>
+      <c r="I92" s="4">
+        <v>46112</v>
+      </c>
+      <c r="J92" s="3">
+        <v>3</v>
+      </c>
+      <c r="K92" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="L92" s="3">
+        <v>4004</v>
+      </c>
+      <c r="M92" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="N92" s="3"/>
+      <c r="O92" s="3"/>
+      <c r="P92" s="3"/>
+      <c r="Q92" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A93" s="2"/>
+      <c r="B93" s="3">
+        <v>8</v>
+      </c>
+      <c r="C93" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D93" s="3">
+        <v>26031972</v>
+      </c>
+      <c r="E93" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="F93" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="G93" s="4">
+        <v>46098</v>
+      </c>
+      <c r="H93" s="4">
+        <v>46099</v>
+      </c>
+      <c r="I93" s="4">
+        <v>46112</v>
+      </c>
+      <c r="J93" s="3">
+        <v>3</v>
+      </c>
+      <c r="K93" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="L93" s="3">
+        <v>1269</v>
+      </c>
+      <c r="M93" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="N93" s="3"/>
+      <c r="O93" s="3"/>
+      <c r="P93" s="3"/>
+      <c r="Q93" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A94" s="2"/>
+      <c r="B94" s="3">
+        <v>8</v>
+      </c>
+      <c r="C94" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D94" s="3">
+        <v>26031972</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="G94" s="4">
+        <v>46098</v>
+      </c>
+      <c r="H94" s="4">
+        <v>46099</v>
+      </c>
+      <c r="I94" s="4">
+        <v>46112</v>
+      </c>
+      <c r="J94" s="3">
+        <v>3</v>
+      </c>
+      <c r="K94" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="L94" s="3">
+        <v>1187</v>
+      </c>
+      <c r="M94" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="N94" s="3"/>
+      <c r="O94" s="3"/>
+      <c r="P94" s="3"/>
+      <c r="Q94" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A95" s="2"/>
+      <c r="B95" s="3">
+        <v>8</v>
+      </c>
+      <c r="C95" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D95" s="3">
+        <v>26031972</v>
+      </c>
+      <c r="E95" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="F95" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="G95" s="4">
+        <v>46098</v>
+      </c>
+      <c r="H95" s="4">
+        <v>46099</v>
+      </c>
+      <c r="I95" s="4">
+        <v>46112</v>
+      </c>
+      <c r="J95" s="3">
+        <v>3</v>
+      </c>
+      <c r="K95" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="L95" s="3">
+        <v>1185</v>
+      </c>
+      <c r="M95" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="N95" s="3"/>
+      <c r="O95" s="3"/>
+      <c r="P95" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q95" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A96" s="2"/>
+      <c r="B96" s="3">
+        <v>8</v>
+      </c>
+      <c r="C96" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D96" s="3">
+        <v>26031972</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="G96" s="4">
+        <v>46098</v>
+      </c>
+      <c r="H96" s="4">
+        <v>46099</v>
+      </c>
+      <c r="I96" s="4">
+        <v>46112</v>
+      </c>
+      <c r="J96" s="3">
+        <v>3</v>
+      </c>
+      <c r="K96" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="L96" s="3">
+        <v>1290</v>
+      </c>
+      <c r="M96" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="N96" s="3"/>
+      <c r="O96" s="3"/>
+      <c r="P96" s="3"/>
+      <c r="Q96" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A97" s="2"/>
+      <c r="B97" s="3">
+        <v>8</v>
+      </c>
+      <c r="C97" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D97" s="3">
+        <v>26031972</v>
+      </c>
+      <c r="E97" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="F97" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="G97" s="4">
+        <v>46098</v>
+      </c>
+      <c r="H97" s="4">
+        <v>46099</v>
+      </c>
+      <c r="I97" s="4">
+        <v>46112</v>
+      </c>
+      <c r="J97" s="3">
+        <v>3</v>
+      </c>
+      <c r="K97" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="L97" s="3">
+        <v>1175</v>
+      </c>
+      <c r="M97" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="N97" s="3"/>
+      <c r="O97" s="3"/>
+      <c r="P97" s="3"/>
+      <c r="Q97" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A98" s="2"/>
+      <c r="B98" s="3">
+        <v>8</v>
+      </c>
+      <c r="C98" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D98" s="3">
+        <v>26031972</v>
+      </c>
+      <c r="E98" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="F98" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="G98" s="4">
+        <v>46098</v>
+      </c>
+      <c r="H98" s="4">
+        <v>46099</v>
+      </c>
+      <c r="I98" s="4">
+        <v>46112</v>
+      </c>
+      <c r="J98" s="3">
+        <v>3</v>
+      </c>
+      <c r="K98" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="L98" s="3">
+        <v>1060</v>
+      </c>
+      <c r="M98" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="N98" s="3"/>
+      <c r="O98" s="3"/>
+      <c r="P98" s="3"/>
+      <c r="Q98" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A99" s="2"/>
+      <c r="B99" s="3">
+        <v>8</v>
+      </c>
+      <c r="C99" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D99" s="3">
+        <v>26031972</v>
+      </c>
+      <c r="E99" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="F99" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="G99" s="4">
+        <v>46098</v>
+      </c>
+      <c r="H99" s="4">
+        <v>46099</v>
+      </c>
+      <c r="I99" s="4">
+        <v>46112</v>
+      </c>
+      <c r="J99" s="3">
+        <v>3</v>
+      </c>
+      <c r="K99" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="L99" s="3">
+        <v>1066</v>
+      </c>
+      <c r="M99" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="N99" s="3"/>
+      <c r="O99" s="3"/>
+      <c r="P99" s="3"/>
+      <c r="Q99" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A100" s="2"/>
+      <c r="B100" s="3">
+        <v>8</v>
+      </c>
+      <c r="C100" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D100" s="3">
+        <v>26031972</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="F100" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="G100" s="4">
+        <v>46098</v>
+      </c>
+      <c r="H100" s="4">
+        <v>46099</v>
+      </c>
+      <c r="I100" s="4">
+        <v>46112</v>
+      </c>
+      <c r="J100" s="3">
+        <v>3</v>
+      </c>
+      <c r="K100" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="L100" s="3">
+        <v>1294</v>
+      </c>
+      <c r="M100" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="N100" s="3"/>
+      <c r="O100" s="3"/>
+      <c r="P100" s="3"/>
+      <c r="Q100" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A101" s="2"/>
+      <c r="B101" s="3">
+        <v>8</v>
+      </c>
+      <c r="C101" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D101" s="3">
+        <v>26031972</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="G101" s="4">
+        <v>46098</v>
+      </c>
+      <c r="H101" s="4">
+        <v>46099</v>
+      </c>
+      <c r="I101" s="4">
+        <v>46112</v>
+      </c>
+      <c r="J101" s="3">
+        <v>3</v>
+      </c>
+      <c r="K101" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="L101" s="3">
+        <v>1266</v>
+      </c>
+      <c r="M101" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="N101" s="3"/>
+      <c r="O101" s="3"/>
+      <c r="P101" s="3"/>
+      <c r="Q101" s="3" t="b">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Pittsburgh WIP Data/WIP Data Import Template.xlsx
+++ b/Pittsburgh WIP Data/WIP Data Import Template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://spllabs-my.sharepoint.com/personal/jonathan_john_spl-inc_com/Documents/Dev/Pitt Lab WIP Dashboard/Pittsburgh WIP Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="11_E9006845ED4581FB0A9CD559D460A3FB778B3E7F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{689D8F30-B208-4E02-93B6-991B3225C2F1}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="11_E9006845ED4581FB0A9CD559D460A3FB778B3E7F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{35028224-3CBC-4ACD-BDA8-0869F32CF4C0}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="588" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="463" uniqueCount="102">
   <si>
     <t>Due Days</t>
   </si>
@@ -81,33 +81,9 @@
     <t>EOG22</t>
   </si>
   <si>
-    <t>Oil</t>
-  </si>
-  <si>
-    <t>EOS-VP</t>
-  </si>
-  <si>
     <t>001A</t>
   </si>
   <si>
-    <t>Cylinder piston 500cc</t>
-  </si>
-  <si>
-    <t>2500-00873</t>
-  </si>
-  <si>
-    <t>GC-C10LIQ</t>
-  </si>
-  <si>
-    <t>WILLIAMS</t>
-  </si>
-  <si>
-    <t>Liquid</t>
-  </si>
-  <si>
-    <t>Report sent 3.12.2026</t>
-  </si>
-  <si>
     <t>GC-C6GAS</t>
   </si>
   <si>
@@ -120,39 +96,21 @@
     <t>Cylinder 300cc</t>
   </si>
   <si>
-    <t>1111-013068</t>
-  </si>
-  <si>
     <t>Gas</t>
   </si>
   <si>
     <t>003A</t>
   </si>
   <si>
-    <t>1111-010246</t>
-  </si>
-  <si>
     <t>004A</t>
   </si>
   <si>
-    <t>1111-010813</t>
-  </si>
-  <si>
-    <t>1111-012940</t>
-  </si>
-  <si>
     <t>006A</t>
   </si>
   <si>
-    <t>1111-013139</t>
-  </si>
-  <si>
     <t>007A</t>
   </si>
   <si>
-    <t>3040-02216</t>
-  </si>
-  <si>
     <t>008A</t>
   </si>
   <si>
@@ -240,9 +198,6 @@
     <t>022A</t>
   </si>
   <si>
-    <t>1111-013034</t>
-  </si>
-  <si>
     <t>023A</t>
   </si>
   <si>
@@ -261,39 +216,12 @@
     <t>1111-010840</t>
   </si>
   <si>
-    <t>1111-010233</t>
-  </si>
-  <si>
-    <t>1111-012458</t>
-  </si>
-  <si>
-    <t>1111-013193</t>
-  </si>
-  <si>
-    <t>1111-012453</t>
-  </si>
-  <si>
-    <t>1111-012499</t>
-  </si>
-  <si>
-    <t>1111-010790</t>
-  </si>
-  <si>
-    <t>1111-012501</t>
-  </si>
-  <si>
-    <t>1111-012498</t>
-  </si>
-  <si>
     <t>1111-012490</t>
   </si>
   <si>
     <t>1111-010691</t>
   </si>
   <si>
-    <t>1111-010220</t>
-  </si>
-  <si>
     <t>1111-012509</t>
   </si>
   <si>
@@ -301,9 +229,6 @@
   </si>
   <si>
     <t>1111-013023</t>
-  </si>
-  <si>
-    <t>1111-010228</t>
   </si>
   <si>
     <t>1111-010663</t>
@@ -523,6 +448,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -798,40 +727,40 @@
         <v>19</v>
       </c>
       <c r="D2" s="3">
-        <v>26031372</v>
+        <v>26030964</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="G2" s="4">
-        <v>46094</v>
+        <v>46090</v>
       </c>
       <c r="H2" s="4">
-        <v>46094</v>
+        <v>46091</v>
       </c>
       <c r="I2" s="4">
-        <v>46097</v>
+        <v>46098</v>
       </c>
       <c r="J2" s="3">
         <v>3</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="N2" s="3"/>
       <c r="O2" s="3"/>
       <c r="P2" s="3"/>
       <c r="Q2" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -840,37 +769,37 @@
         <v>-6</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D3" s="3">
-        <v>26031372</v>
+        <v>26030964</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="G3" s="4">
-        <v>46094</v>
+        <v>46090</v>
       </c>
       <c r="H3" s="4">
-        <v>46094</v>
+        <v>46091</v>
       </c>
       <c r="I3" s="4">
-        <v>46097</v>
+        <v>46098</v>
       </c>
       <c r="J3" s="3">
         <v>3</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="N3" s="3"/>
       <c r="O3" s="3"/>
@@ -882,40 +811,40 @@
     <row r="4" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2"/>
       <c r="B4" s="3">
-        <v>-4</v>
+        <v>-6</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D4" s="3">
-        <v>26031154</v>
+        <v>26030964</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="G4" s="4">
-        <v>46092</v>
+        <v>46090</v>
       </c>
       <c r="H4" s="4">
-        <v>46093</v>
+        <v>46091</v>
       </c>
       <c r="I4" s="4">
-        <v>46099</v>
+        <v>46098</v>
       </c>
       <c r="J4" s="3">
         <v>3</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L4" s="3">
-        <v>95402</v>
+        <v>22</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>33</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="N4" s="3"/>
       <c r="O4" s="3"/>
@@ -927,45 +856,43 @@
     <row r="5" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2"/>
       <c r="B5" s="3">
-        <v>-4</v>
+        <v>-6</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D5" s="3">
-        <v>26031155</v>
+        <v>26030964</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="G5" s="4">
-        <v>46092</v>
+        <v>46090</v>
       </c>
       <c r="H5" s="4">
-        <v>46093</v>
+        <v>46091</v>
       </c>
       <c r="I5" s="4">
-        <v>46099</v>
+        <v>46098</v>
       </c>
       <c r="J5" s="3">
         <v>3</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L5" s="3">
-        <v>96237</v>
+        <v>22</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>35</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="N5" s="3"/>
-      <c r="O5" s="3" t="s">
-        <v>26</v>
-      </c>
+      <c r="O5" s="3"/>
       <c r="P5" s="3"/>
       <c r="Q5" s="3" t="b">
         <v>1</v>
@@ -974,19 +901,19 @@
     <row r="6" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2"/>
       <c r="B6" s="3">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="D6" s="3">
         <v>26030964</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="G6" s="4">
         <v>46090</v>
@@ -1001,37 +928,37 @@
         <v>3</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="N6" s="3"/>
       <c r="O6" s="3"/>
       <c r="P6" s="3"/>
       <c r="Q6" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2"/>
       <c r="B7" s="3">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="D7" s="3">
         <v>26030964</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="G7" s="4">
         <v>46090</v>
@@ -1046,13 +973,13 @@
         <v>3</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="N7" s="3"/>
       <c r="O7" s="3"/>
@@ -1064,19 +991,19 @@
     <row r="8" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2"/>
       <c r="B8" s="3">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="D8" s="3">
         <v>26030964</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="G8" s="4">
         <v>46090</v>
@@ -1091,37 +1018,37 @@
         <v>3</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="N8" s="3"/>
       <c r="O8" s="3"/>
       <c r="P8" s="3"/>
       <c r="Q8" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2"/>
       <c r="B9" s="3">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="D9" s="3">
         <v>26030964</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="G9" s="4">
         <v>46090</v>
@@ -1136,37 +1063,37 @@
         <v>3</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="N9" s="3"/>
       <c r="O9" s="3"/>
       <c r="P9" s="3"/>
       <c r="Q9" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2"/>
       <c r="B10" s="3">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="D10" s="3">
         <v>26030964</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="G10" s="4">
         <v>46090</v>
@@ -1181,37 +1108,37 @@
         <v>3</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="N10" s="3"/>
       <c r="O10" s="3"/>
       <c r="P10" s="3"/>
       <c r="Q10" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2"/>
       <c r="B11" s="3">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="D11" s="3">
         <v>26030964</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="G11" s="4">
         <v>46090</v>
@@ -1226,37 +1153,37 @@
         <v>3</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2"/>
       <c r="B12" s="3">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="D12" s="3">
         <v>26030964</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="G12" s="4">
         <v>46090</v>
@@ -1271,37 +1198,37 @@
         <v>3</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="N12" s="3"/>
       <c r="O12" s="3"/>
       <c r="P12" s="3"/>
       <c r="Q12" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2"/>
       <c r="B13" s="3">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="D13" s="3">
         <v>26030964</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="G13" s="4">
         <v>46090</v>
@@ -1316,37 +1243,37 @@
         <v>3</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="N13" s="3"/>
       <c r="O13" s="3"/>
       <c r="P13" s="3"/>
       <c r="Q13" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2"/>
       <c r="B14" s="3">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="D14" s="3">
         <v>26030964</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="G14" s="4">
         <v>46090</v>
@@ -1361,37 +1288,37 @@
         <v>3</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="N14" s="3"/>
       <c r="O14" s="3"/>
       <c r="P14" s="3"/>
       <c r="Q14" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2"/>
       <c r="B15" s="3">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="D15" s="3">
         <v>26030964</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="G15" s="4">
         <v>46090</v>
@@ -1406,37 +1333,37 @@
         <v>3</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="L15" s="3" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="N15" s="3"/>
       <c r="O15" s="3"/>
       <c r="P15" s="3"/>
       <c r="Q15" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2"/>
       <c r="B16" s="3">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="D16" s="3">
         <v>26030964</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="G16" s="4">
         <v>46090</v>
@@ -1451,37 +1378,37 @@
         <v>3</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="L16" s="3" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2"/>
       <c r="B17" s="3">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="D17" s="3">
         <v>26030964</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="G17" s="4">
         <v>46090</v>
@@ -1496,37 +1423,37 @@
         <v>3</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="L17" s="3" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="N17" s="3"/>
       <c r="O17" s="3"/>
       <c r="P17" s="3"/>
       <c r="Q17" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2"/>
       <c r="B18" s="3">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="D18" s="3">
         <v>26030964</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="G18" s="4">
         <v>46090</v>
@@ -1541,37 +1468,37 @@
         <v>3</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="L18" s="3" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="N18" s="3"/>
       <c r="O18" s="3"/>
       <c r="P18" s="3"/>
       <c r="Q18" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2"/>
       <c r="B19" s="3">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="D19" s="3">
-        <v>26030964</v>
+        <v>26030966</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="G19" s="4">
         <v>46090</v>
@@ -1580,43 +1507,43 @@
         <v>46091</v>
       </c>
       <c r="I19" s="4">
-        <v>46098</v>
+        <v>46104</v>
       </c>
       <c r="J19" s="3">
         <v>3</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="L19" s="3" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2"/>
       <c r="B20" s="3">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="D20" s="3">
-        <v>26030964</v>
+        <v>26030966</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="G20" s="4">
         <v>46090</v>
@@ -1625,43 +1552,43 @@
         <v>46091</v>
       </c>
       <c r="I20" s="4">
-        <v>46098</v>
+        <v>46104</v>
       </c>
       <c r="J20" s="3">
         <v>3</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="L20" s="3" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="N20" s="3"/>
       <c r="O20" s="3"/>
       <c r="P20" s="3"/>
       <c r="Q20" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2"/>
       <c r="B21" s="3">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="D21" s="3">
-        <v>26030964</v>
+        <v>26030966</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="G21" s="4">
         <v>46090</v>
@@ -1670,43 +1597,43 @@
         <v>46091</v>
       </c>
       <c r="I21" s="4">
-        <v>46098</v>
+        <v>46104</v>
       </c>
       <c r="J21" s="3">
         <v>3</v>
       </c>
       <c r="K21" s="3" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="L21" s="3" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="N21" s="3"/>
       <c r="O21" s="3"/>
       <c r="P21" s="3"/>
       <c r="Q21" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2"/>
       <c r="B22" s="3">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="D22" s="3">
-        <v>26030964</v>
+        <v>26030966</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="G22" s="4">
         <v>46090</v>
@@ -1715,43 +1642,43 @@
         <v>46091</v>
       </c>
       <c r="I22" s="4">
-        <v>46098</v>
+        <v>46104</v>
       </c>
       <c r="J22" s="3">
         <v>3</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="L22" s="3" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="N22" s="3"/>
       <c r="O22" s="3"/>
       <c r="P22" s="3"/>
       <c r="Q22" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2"/>
       <c r="B23" s="3">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="D23" s="3">
-        <v>26030964</v>
+        <v>26030966</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="G23" s="4">
         <v>46090</v>
@@ -1760,43 +1687,43 @@
         <v>46091</v>
       </c>
       <c r="I23" s="4">
-        <v>46098</v>
+        <v>46104</v>
       </c>
       <c r="J23" s="3">
         <v>3</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="L23" s="3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="M23" s="3" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="N23" s="3"/>
       <c r="O23" s="3"/>
       <c r="P23" s="3"/>
       <c r="Q23" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2"/>
       <c r="B24" s="3">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>26030964</v>
+        <v>26030966</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="G24" s="4">
         <v>46090</v>
@@ -1805,43 +1732,43 @@
         <v>46091</v>
       </c>
       <c r="I24" s="4">
-        <v>46098</v>
+        <v>46104</v>
       </c>
       <c r="J24" s="3">
         <v>3</v>
       </c>
       <c r="K24" s="3" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="L24" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M24" s="3" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="N24" s="3"/>
       <c r="O24" s="3"/>
       <c r="P24" s="3"/>
       <c r="Q24" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2"/>
       <c r="B25" s="3">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="D25" s="3">
-        <v>26030964</v>
+        <v>26030966</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="G25" s="4">
         <v>46090</v>
@@ -1850,19 +1777,19 @@
         <v>46091</v>
       </c>
       <c r="I25" s="4">
-        <v>46098</v>
+        <v>46104</v>
       </c>
       <c r="J25" s="3">
         <v>3</v>
       </c>
       <c r="K25" s="3" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="L25" s="3" t="s">
         <v>69</v>
       </c>
       <c r="M25" s="3" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="N25" s="3"/>
       <c r="O25" s="3"/>
@@ -1874,19 +1801,19 @@
     <row r="26" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2"/>
       <c r="B26" s="3">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="D26" s="3">
-        <v>26030964</v>
+        <v>26030966</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="G26" s="4">
         <v>46090</v>
@@ -1895,64 +1822,64 @@
         <v>46091</v>
       </c>
       <c r="I26" s="4">
-        <v>46098</v>
+        <v>46104</v>
       </c>
       <c r="J26" s="3">
         <v>3</v>
       </c>
       <c r="K26" s="3" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="L26" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="M26" s="3" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="N26" s="3"/>
       <c r="O26" s="3"/>
       <c r="P26" s="3"/>
       <c r="Q26" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2"/>
       <c r="B27" s="3">
-        <v>-5</v>
+        <v>3</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="D27" s="3">
-        <v>26030964</v>
+        <v>26031383</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>72</v>
+        <v>18</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="G27" s="4">
-        <v>46090</v>
+        <v>46094</v>
       </c>
       <c r="H27" s="4">
-        <v>46091</v>
+        <v>46094</v>
       </c>
       <c r="I27" s="4">
-        <v>46098</v>
+        <v>46108</v>
       </c>
       <c r="J27" s="3">
         <v>3</v>
       </c>
       <c r="K27" s="3" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="L27" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="M27" s="3" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="N27" s="3"/>
       <c r="O27" s="3"/>
@@ -1964,40 +1891,40 @@
     <row r="28" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2"/>
       <c r="B28" s="3">
-        <v>-5</v>
+        <v>3</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="D28" s="3">
-        <v>26030964</v>
+        <v>26031383</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>74</v>
+        <v>20</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="G28" s="4">
-        <v>46090</v>
+        <v>46094</v>
       </c>
       <c r="H28" s="4">
-        <v>46091</v>
+        <v>46094</v>
       </c>
       <c r="I28" s="4">
-        <v>46098</v>
+        <v>46108</v>
       </c>
       <c r="J28" s="3">
         <v>3</v>
       </c>
       <c r="K28" s="3" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="L28" s="3" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="M28" s="3" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="N28" s="3"/>
       <c r="O28" s="3"/>
@@ -2009,40 +1936,40 @@
     <row r="29" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2"/>
       <c r="B29" s="3">
-        <v>-5</v>
+        <v>3</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="D29" s="3">
-        <v>26030964</v>
+        <v>26031383</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>76</v>
+        <v>24</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="G29" s="4">
-        <v>46090</v>
+        <v>46094</v>
       </c>
       <c r="H29" s="4">
-        <v>46091</v>
+        <v>46094</v>
       </c>
       <c r="I29" s="4">
-        <v>46098</v>
+        <v>46108</v>
       </c>
       <c r="J29" s="3">
         <v>3</v>
       </c>
       <c r="K29" s="3" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="L29" s="3" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="M29" s="3" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="N29" s="3"/>
       <c r="O29" s="3"/>
@@ -2054,40 +1981,40 @@
     <row r="30" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2"/>
       <c r="B30" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="D30" s="3">
-        <v>26030966</v>
+        <v>26031383</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="G30" s="4">
-        <v>46090</v>
+        <v>46094</v>
       </c>
       <c r="H30" s="4">
-        <v>46091</v>
+        <v>46094</v>
       </c>
       <c r="I30" s="4">
-        <v>46104</v>
+        <v>46108</v>
       </c>
       <c r="J30" s="3">
         <v>3</v>
       </c>
       <c r="K30" s="3" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="L30" s="3" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="M30" s="3" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="N30" s="3"/>
       <c r="O30" s="3"/>
@@ -2099,40 +2026,40 @@
     <row r="31" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2"/>
       <c r="B31" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="D31" s="3">
-        <v>26030966</v>
+        <v>26031383</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>44</v>
+        <v>16</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="G31" s="4">
-        <v>46090</v>
+        <v>46094</v>
       </c>
       <c r="H31" s="4">
-        <v>46091</v>
+        <v>46094</v>
       </c>
       <c r="I31" s="4">
-        <v>46104</v>
+        <v>46108</v>
       </c>
       <c r="J31" s="3">
         <v>3</v>
       </c>
       <c r="K31" s="3" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="L31" s="3" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="M31" s="3" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="N31" s="3"/>
       <c r="O31" s="3"/>
@@ -2144,40 +2071,40 @@
     <row r="32" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2"/>
       <c r="B32" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="D32" s="3">
-        <v>26030966</v>
+        <v>26031383</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="G32" s="4">
-        <v>46090</v>
+        <v>46094</v>
       </c>
       <c r="H32" s="4">
-        <v>46091</v>
+        <v>46094</v>
       </c>
       <c r="I32" s="4">
-        <v>46104</v>
+        <v>46108</v>
       </c>
       <c r="J32" s="3">
         <v>3</v>
       </c>
       <c r="K32" s="3" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="L32" s="3" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="M32" s="3" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="N32" s="3"/>
       <c r="O32" s="3"/>
@@ -2189,40 +2116,40 @@
     <row r="33" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2"/>
       <c r="B33" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C33" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D33" s="3">
+        <v>26031383</v>
+      </c>
+      <c r="E33" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="D33" s="3">
-        <v>26030966</v>
-      </c>
-      <c r="E33" s="3" t="s">
-        <v>48</v>
-      </c>
       <c r="F33" s="3" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="G33" s="4">
-        <v>46090</v>
+        <v>46094</v>
       </c>
       <c r="H33" s="4">
-        <v>46091</v>
+        <v>46094</v>
       </c>
       <c r="I33" s="4">
-        <v>46104</v>
+        <v>46108</v>
       </c>
       <c r="J33" s="3">
         <v>3</v>
       </c>
       <c r="K33" s="3" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="L33" s="3" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="M33" s="3" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="N33" s="3"/>
       <c r="O33" s="3"/>
@@ -2234,40 +2161,40 @@
     <row r="34" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2"/>
       <c r="B34" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="D34" s="3">
-        <v>26030966</v>
+        <v>26031383</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="G34" s="4">
-        <v>46090</v>
+        <v>46094</v>
       </c>
       <c r="H34" s="4">
-        <v>46091</v>
+        <v>46094</v>
       </c>
       <c r="I34" s="4">
-        <v>46104</v>
+        <v>46108</v>
       </c>
       <c r="J34" s="3">
         <v>3</v>
       </c>
       <c r="K34" s="3" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="L34" s="3" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="M34" s="3" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="N34" s="3"/>
       <c r="O34" s="3"/>
@@ -2279,40 +2206,40 @@
     <row r="35" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2"/>
       <c r="B35" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="D35" s="3">
-        <v>26030966</v>
+        <v>26031383</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="G35" s="4">
-        <v>46090</v>
+        <v>46094</v>
       </c>
       <c r="H35" s="4">
-        <v>46091</v>
+        <v>46094</v>
       </c>
       <c r="I35" s="4">
-        <v>46104</v>
+        <v>46108</v>
       </c>
       <c r="J35" s="3">
         <v>3</v>
       </c>
       <c r="K35" s="3" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="L35" s="3" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="M35" s="3" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="N35" s="3"/>
       <c r="O35" s="3"/>
@@ -2324,40 +2251,40 @@
     <row r="36" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2"/>
       <c r="B36" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="D36" s="3">
-        <v>26030966</v>
+        <v>26031383</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>54</v>
+        <v>32</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="G36" s="4">
-        <v>46090</v>
+        <v>46094</v>
       </c>
       <c r="H36" s="4">
-        <v>46091</v>
+        <v>46094</v>
       </c>
       <c r="I36" s="4">
-        <v>46104</v>
+        <v>46108</v>
       </c>
       <c r="J36" s="3">
         <v>3</v>
       </c>
       <c r="K36" s="3" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="L36" s="3" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="M36" s="3" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="N36" s="3"/>
       <c r="O36" s="3"/>
@@ -2369,40 +2296,40 @@
     <row r="37" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2"/>
       <c r="B37" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="D37" s="3">
-        <v>26030966</v>
+        <v>26031383</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>56</v>
+        <v>34</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="G37" s="4">
-        <v>46090</v>
+        <v>46094</v>
       </c>
       <c r="H37" s="4">
-        <v>46091</v>
+        <v>46094</v>
       </c>
       <c r="I37" s="4">
-        <v>46104</v>
+        <v>46108</v>
       </c>
       <c r="J37" s="3">
         <v>3</v>
       </c>
       <c r="K37" s="3" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="L37" s="3" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="M37" s="3" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="N37" s="3"/>
       <c r="O37" s="3"/>
@@ -2414,40 +2341,40 @@
     <row r="38" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2"/>
       <c r="B38" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="D38" s="3">
-        <v>26030966</v>
+        <v>26032281</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>58</v>
+        <v>20</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="G38" s="4">
-        <v>46090</v>
+        <v>46100</v>
       </c>
       <c r="H38" s="4">
-        <v>46091</v>
+        <v>46100</v>
       </c>
       <c r="I38" s="4">
-        <v>46104</v>
+        <v>46108</v>
       </c>
       <c r="J38" s="3">
         <v>3</v>
       </c>
       <c r="K38" s="3" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="L38" s="3" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="M38" s="3" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="N38" s="3"/>
       <c r="O38" s="3"/>
@@ -2459,40 +2386,40 @@
     <row r="39" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2"/>
       <c r="B39" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="D39" s="3">
-        <v>26030966</v>
+        <v>26032281</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>60</v>
+        <v>24</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="G39" s="4">
-        <v>46090</v>
+        <v>46100</v>
       </c>
       <c r="H39" s="4">
-        <v>46091</v>
+        <v>46100</v>
       </c>
       <c r="I39" s="4">
-        <v>46104</v>
+        <v>46108</v>
       </c>
       <c r="J39" s="3">
         <v>3</v>
       </c>
       <c r="K39" s="3" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="L39" s="3" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M39" s="3" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
@@ -2504,40 +2431,40 @@
     <row r="40" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2"/>
       <c r="B40" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="D40" s="3">
-        <v>26030966</v>
+        <v>26032281</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>62</v>
+        <v>25</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="G40" s="4">
-        <v>46090</v>
+        <v>46100</v>
       </c>
       <c r="H40" s="4">
-        <v>46091</v>
+        <v>46100</v>
       </c>
       <c r="I40" s="4">
-        <v>46104</v>
+        <v>46108</v>
       </c>
       <c r="J40" s="3">
         <v>3</v>
       </c>
       <c r="K40" s="3" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="L40" s="3" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="M40" s="3" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
@@ -2549,40 +2476,40 @@
     <row r="41" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2"/>
       <c r="B41" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="D41" s="3">
-        <v>26030966</v>
+        <v>26032281</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>64</v>
+        <v>16</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="G41" s="4">
-        <v>46090</v>
+        <v>46100</v>
       </c>
       <c r="H41" s="4">
-        <v>46091</v>
+        <v>46100</v>
       </c>
       <c r="I41" s="4">
-        <v>46104</v>
+        <v>46108</v>
       </c>
       <c r="J41" s="3">
         <v>3</v>
       </c>
       <c r="K41" s="3" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="L41" s="3" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="M41" s="3" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="N41" s="3"/>
       <c r="O41" s="3"/>
@@ -2594,40 +2521,40 @@
     <row r="42" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2"/>
       <c r="B42" s="3">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="D42" s="3">
-        <v>26030966</v>
+        <v>26032652</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>66</v>
+        <v>18</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="G42" s="4">
-        <v>46090</v>
+        <v>46101</v>
       </c>
       <c r="H42" s="4">
-        <v>46091</v>
+        <v>46101</v>
       </c>
       <c r="I42" s="4">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="J42" s="3">
         <v>3</v>
       </c>
       <c r="K42" s="3" t="s">
-        <v>30</v>
+        <v>86</v>
       </c>
       <c r="L42" s="3" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="M42" s="3" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="N42" s="3"/>
       <c r="O42" s="3"/>
@@ -2639,40 +2566,40 @@
     <row r="43" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="2"/>
       <c r="B43" s="3">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="D43" s="3">
-        <v>26030966</v>
+        <v>26032652</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>68</v>
+        <v>20</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="G43" s="4">
-        <v>46090</v>
+        <v>46101</v>
       </c>
       <c r="H43" s="4">
-        <v>46091</v>
+        <v>46101</v>
       </c>
       <c r="I43" s="4">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="J43" s="3">
         <v>3</v>
       </c>
       <c r="K43" s="3" t="s">
-        <v>30</v>
+        <v>86</v>
       </c>
       <c r="L43" s="3" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="M43" s="3" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="N43" s="3"/>
       <c r="O43" s="3"/>
@@ -2684,40 +2611,40 @@
     <row r="44" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="2"/>
       <c r="B44" s="3">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="D44" s="3">
-        <v>26030966</v>
+        <v>26032652</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>70</v>
+        <v>24</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="G44" s="4">
-        <v>46090</v>
+        <v>46101</v>
       </c>
       <c r="H44" s="4">
-        <v>46091</v>
+        <v>46101</v>
       </c>
       <c r="I44" s="4">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="J44" s="3">
         <v>3</v>
       </c>
       <c r="K44" s="3" t="s">
-        <v>30</v>
+        <v>86</v>
       </c>
       <c r="L44" s="3" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="M44" s="3" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="N44" s="3"/>
       <c r="O44" s="3"/>
@@ -2729,40 +2656,40 @@
     <row r="45" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2"/>
       <c r="B45" s="3">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="D45" s="3">
-        <v>26030966</v>
+        <v>26032652</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>72</v>
+        <v>25</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="G45" s="4">
-        <v>46090</v>
+        <v>46101</v>
       </c>
       <c r="H45" s="4">
-        <v>46091</v>
+        <v>46101</v>
       </c>
       <c r="I45" s="4">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="J45" s="3">
         <v>3</v>
       </c>
       <c r="K45" s="3" t="s">
-        <v>30</v>
+        <v>86</v>
       </c>
       <c r="L45" s="3" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="M45" s="3" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="N45" s="3"/>
       <c r="O45" s="3"/>
@@ -2774,40 +2701,40 @@
     <row r="46" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2"/>
       <c r="B46" s="3">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="D46" s="3">
-        <v>26030966</v>
+        <v>26032652</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>74</v>
+        <v>16</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="G46" s="4">
-        <v>46090</v>
+        <v>46101</v>
       </c>
       <c r="H46" s="4">
-        <v>46091</v>
+        <v>46101</v>
       </c>
       <c r="I46" s="4">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="J46" s="3">
         <v>3</v>
       </c>
       <c r="K46" s="3" t="s">
-        <v>30</v>
+        <v>86</v>
       </c>
       <c r="L46" s="3" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="M46" s="3" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="N46" s="3"/>
       <c r="O46" s="3"/>
@@ -2819,40 +2746,36 @@
     <row r="47" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2"/>
       <c r="B47" s="3">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="D47" s="3">
-        <v>26030966</v>
+        <v>26032652</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>76</v>
+        <v>26</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="G47" s="4">
-        <v>46090</v>
+        <v>46101</v>
       </c>
       <c r="H47" s="4">
-        <v>46091</v>
+        <v>46101</v>
       </c>
       <c r="I47" s="4">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="J47" s="3">
         <v>3</v>
       </c>
-      <c r="K47" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="L47" s="3" t="s">
-        <v>95</v>
-      </c>
+      <c r="K47" s="3"/>
+      <c r="L47" s="3"/>
       <c r="M47" s="3" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="N47" s="3"/>
       <c r="O47" s="3"/>
@@ -2864,40 +2787,40 @@
     <row r="48" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="2"/>
       <c r="B48" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C48" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D48" s="3">
+        <v>26032652</v>
+      </c>
+      <c r="E48" s="3" t="s">
         <v>27</v>
-      </c>
-      <c r="D48" s="3">
-        <v>26031383</v>
-      </c>
-      <c r="E48" s="3" t="s">
-        <v>20</v>
       </c>
       <c r="F48" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G48" s="4">
-        <v>46094</v>
+        <v>46101</v>
       </c>
       <c r="H48" s="4">
-        <v>46094</v>
+        <v>46101</v>
       </c>
       <c r="I48" s="4">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="J48" s="3">
         <v>3</v>
       </c>
       <c r="K48" s="3" t="s">
-        <v>30</v>
+        <v>86</v>
       </c>
       <c r="L48" s="3" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="M48" s="3" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="N48" s="3"/>
       <c r="O48" s="3"/>
@@ -2909,13 +2832,13 @@
     <row r="49" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="2"/>
       <c r="B49" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="D49" s="3">
-        <v>26031383</v>
+        <v>26032652</v>
       </c>
       <c r="E49" s="3" t="s">
         <v>28</v>
@@ -2924,25 +2847,25 @@
         <v>17</v>
       </c>
       <c r="G49" s="4">
-        <v>46094</v>
+        <v>46101</v>
       </c>
       <c r="H49" s="4">
-        <v>46094</v>
+        <v>46101</v>
       </c>
       <c r="I49" s="4">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="J49" s="3">
         <v>3</v>
       </c>
       <c r="K49" s="3" t="s">
-        <v>30</v>
+        <v>86</v>
       </c>
       <c r="L49" s="3" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="M49" s="3" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="N49" s="3"/>
       <c r="O49" s="3"/>
@@ -2954,40 +2877,40 @@
     <row r="50" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="2"/>
       <c r="B50" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="D50" s="3">
-        <v>26031383</v>
+        <v>26032652</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F50" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G50" s="4">
-        <v>46094</v>
+        <v>46101</v>
       </c>
       <c r="H50" s="4">
-        <v>46094</v>
+        <v>46101</v>
       </c>
       <c r="I50" s="4">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="J50" s="3">
         <v>3</v>
       </c>
       <c r="K50" s="3" t="s">
-        <v>30</v>
+        <v>86</v>
       </c>
       <c r="L50" s="3" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="M50" s="3" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="N50" s="3"/>
       <c r="O50" s="3"/>
@@ -2999,40 +2922,40 @@
     <row r="51" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="2"/>
       <c r="B51" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="D51" s="3">
-        <v>26031383</v>
+        <v>26032652</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F51" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G51" s="4">
-        <v>46094</v>
+        <v>46101</v>
       </c>
       <c r="H51" s="4">
-        <v>46094</v>
+        <v>46101</v>
       </c>
       <c r="I51" s="4">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="J51" s="3">
         <v>3</v>
       </c>
       <c r="K51" s="3" t="s">
-        <v>30</v>
+        <v>86</v>
       </c>
       <c r="L51" s="3" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="M51" s="3" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="N51" s="3"/>
       <c r="O51" s="3"/>
@@ -3044,40 +2967,40 @@
     <row r="52" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="2"/>
       <c r="B52" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="D52" s="3">
-        <v>26031383</v>
+        <v>26032652</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="F52" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G52" s="4">
-        <v>46094</v>
+        <v>46101</v>
       </c>
       <c r="H52" s="4">
-        <v>46094</v>
+        <v>46101</v>
       </c>
       <c r="I52" s="4">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="J52" s="3">
         <v>3</v>
       </c>
       <c r="K52" s="3" t="s">
-        <v>30</v>
+        <v>86</v>
       </c>
       <c r="L52" s="3" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="M52" s="3" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="N52" s="3"/>
       <c r="O52" s="3"/>
@@ -3089,40 +3012,40 @@
     <row r="53" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="2"/>
       <c r="B53" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="D53" s="3">
-        <v>26031383</v>
+        <v>26032652</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F53" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G53" s="4">
-        <v>46094</v>
+        <v>46101</v>
       </c>
       <c r="H53" s="4">
-        <v>46094</v>
+        <v>46101</v>
       </c>
       <c r="I53" s="4">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="J53" s="3">
         <v>3</v>
       </c>
       <c r="K53" s="3" t="s">
-        <v>30</v>
+        <v>86</v>
       </c>
       <c r="L53" s="3" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="M53" s="3" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="N53" s="3"/>
       <c r="O53" s="3"/>
@@ -3134,40 +3057,40 @@
     <row r="54" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="2"/>
       <c r="B54" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="D54" s="3">
-        <v>26031383</v>
+        <v>26032652</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F54" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G54" s="4">
-        <v>46094</v>
+        <v>46101</v>
       </c>
       <c r="H54" s="4">
-        <v>46094</v>
+        <v>46101</v>
       </c>
       <c r="I54" s="4">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="J54" s="3">
         <v>3</v>
       </c>
       <c r="K54" s="3" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="L54" s="3" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="M54" s="3" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="N54" s="3"/>
       <c r="O54" s="3"/>
@@ -3179,40 +3102,40 @@
     <row r="55" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="2"/>
       <c r="B55" s="3">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="D55" s="3">
-        <v>26031383</v>
+        <v>26031972</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>17</v>
+        <v>99</v>
       </c>
       <c r="G55" s="4">
-        <v>46094</v>
+        <v>46098</v>
       </c>
       <c r="H55" s="4">
-        <v>46094</v>
+        <v>46099</v>
       </c>
       <c r="I55" s="4">
-        <v>46108</v>
+        <v>46112</v>
       </c>
       <c r="J55" s="3">
         <v>3</v>
       </c>
       <c r="K55" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="L55" s="3" t="s">
-        <v>103</v>
+        <v>22</v>
+      </c>
+      <c r="L55" s="3">
+        <v>1422</v>
       </c>
       <c r="M55" s="3" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
@@ -3224,40 +3147,40 @@
     <row r="56" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="2"/>
       <c r="B56" s="3">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="D56" s="3">
-        <v>26031383</v>
+        <v>26031972</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>17</v>
+        <v>99</v>
       </c>
       <c r="G56" s="4">
-        <v>46094</v>
+        <v>46098</v>
       </c>
       <c r="H56" s="4">
-        <v>46094</v>
+        <v>46099</v>
       </c>
       <c r="I56" s="4">
-        <v>46108</v>
+        <v>46112</v>
       </c>
       <c r="J56" s="3">
         <v>3</v>
       </c>
       <c r="K56" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="L56" s="3" t="s">
-        <v>104</v>
+        <v>22</v>
+      </c>
+      <c r="L56" s="3">
+        <v>1475</v>
       </c>
       <c r="M56" s="3" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
@@ -3269,40 +3192,40 @@
     <row r="57" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="2"/>
       <c r="B57" s="3">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="D57" s="3">
-        <v>26031383</v>
+        <v>26031972</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>46</v>
+        <v>24</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>17</v>
+        <v>99</v>
       </c>
       <c r="G57" s="4">
-        <v>46094</v>
+        <v>46098</v>
       </c>
       <c r="H57" s="4">
-        <v>46094</v>
+        <v>46099</v>
       </c>
       <c r="I57" s="4">
-        <v>46108</v>
+        <v>46112</v>
       </c>
       <c r="J57" s="3">
         <v>3</v>
       </c>
       <c r="K57" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="L57" s="3" t="s">
-        <v>105</v>
+        <v>22</v>
+      </c>
+      <c r="L57" s="3">
+        <v>4755</v>
       </c>
       <c r="M57" s="3" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="N57" s="3"/>
       <c r="O57" s="3"/>
@@ -3314,40 +3237,40 @@
     <row r="58" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="2"/>
       <c r="B58" s="3">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="D58" s="3">
-        <v>26031383</v>
+        <v>26031972</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>48</v>
+        <v>25</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>17</v>
+        <v>99</v>
       </c>
       <c r="G58" s="4">
-        <v>46094</v>
+        <v>46098</v>
       </c>
       <c r="H58" s="4">
-        <v>46094</v>
+        <v>46099</v>
       </c>
       <c r="I58" s="4">
-        <v>46108</v>
+        <v>46112</v>
       </c>
       <c r="J58" s="3">
         <v>3</v>
       </c>
       <c r="K58" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="L58" s="3" t="s">
-        <v>106</v>
+        <v>22</v>
+      </c>
+      <c r="L58" s="3">
+        <v>1301</v>
       </c>
       <c r="M58" s="3" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="N58" s="3"/>
       <c r="O58" s="3"/>
@@ -3359,40 +3282,40 @@
     <row r="59" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="2"/>
       <c r="B59" s="3">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="D59" s="3">
-        <v>26032281</v>
+        <v>26031972</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>17</v>
+        <v>99</v>
       </c>
       <c r="G59" s="4">
-        <v>46100</v>
+        <v>46098</v>
       </c>
       <c r="H59" s="4">
-        <v>46100</v>
+        <v>46099</v>
       </c>
       <c r="I59" s="4">
-        <v>46108</v>
+        <v>46112</v>
       </c>
       <c r="J59" s="3">
         <v>3</v>
       </c>
       <c r="K59" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="L59" s="3" t="s">
-        <v>107</v>
+        <v>22</v>
+      </c>
+      <c r="L59" s="3">
+        <v>1104</v>
       </c>
       <c r="M59" s="3" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="N59" s="3"/>
       <c r="O59" s="3"/>
@@ -3404,40 +3327,40 @@
     <row r="60" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="2"/>
       <c r="B60" s="3">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="D60" s="3">
-        <v>26032281</v>
+        <v>26031972</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>17</v>
+        <v>99</v>
       </c>
       <c r="G60" s="4">
-        <v>46100</v>
+        <v>46098</v>
       </c>
       <c r="H60" s="4">
-        <v>46100</v>
+        <v>46099</v>
       </c>
       <c r="I60" s="4">
-        <v>46108</v>
+        <v>46112</v>
       </c>
       <c r="J60" s="3">
         <v>3</v>
       </c>
       <c r="K60" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="L60" s="3" t="s">
-        <v>108</v>
+        <v>22</v>
+      </c>
+      <c r="L60" s="3">
+        <v>1292</v>
       </c>
       <c r="M60" s="3" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="N60" s="3"/>
       <c r="O60" s="3"/>
@@ -3449,40 +3372,40 @@
     <row r="61" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="2"/>
       <c r="B61" s="3">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C61" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D61" s="3">
+        <v>26031972</v>
+      </c>
+      <c r="E61" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="D61" s="3">
-        <v>26032281</v>
-      </c>
-      <c r="E61" s="3" t="s">
-        <v>35</v>
-      </c>
       <c r="F61" s="3" t="s">
-        <v>17</v>
+        <v>99</v>
       </c>
       <c r="G61" s="4">
-        <v>46100</v>
+        <v>46098</v>
       </c>
       <c r="H61" s="4">
-        <v>46100</v>
+        <v>46099</v>
       </c>
       <c r="I61" s="4">
-        <v>46108</v>
+        <v>46112</v>
       </c>
       <c r="J61" s="3">
         <v>3</v>
       </c>
       <c r="K61" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="L61" s="3" t="s">
-        <v>109</v>
+        <v>22</v>
+      </c>
+      <c r="L61" s="3">
+        <v>1342</v>
       </c>
       <c r="M61" s="3" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="N61" s="3"/>
       <c r="O61" s="3"/>
@@ -3494,40 +3417,40 @@
     <row r="62" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="2"/>
       <c r="B62" s="3">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="D62" s="3">
-        <v>26032281</v>
+        <v>26031972</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>17</v>
+        <v>99</v>
       </c>
       <c r="G62" s="4">
-        <v>46100</v>
+        <v>46098</v>
       </c>
       <c r="H62" s="4">
-        <v>46100</v>
+        <v>46099</v>
       </c>
       <c r="I62" s="4">
-        <v>46108</v>
+        <v>46112</v>
       </c>
       <c r="J62" s="3">
         <v>3</v>
       </c>
       <c r="K62" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="L62" s="3" t="s">
-        <v>110</v>
+        <v>22</v>
+      </c>
+      <c r="L62" s="3">
+        <v>4265</v>
       </c>
       <c r="M62" s="3" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="N62" s="3"/>
       <c r="O62" s="3"/>
@@ -3542,37 +3465,37 @@
         <v>7</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="D63" s="3">
-        <v>26032652</v>
+        <v>26031972</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>17</v>
+        <v>99</v>
       </c>
       <c r="G63" s="4">
-        <v>46101</v>
+        <v>46098</v>
       </c>
       <c r="H63" s="4">
-        <v>46101</v>
+        <v>46099</v>
       </c>
       <c r="I63" s="4">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="J63" s="3">
         <v>3</v>
       </c>
       <c r="K63" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="L63" s="3" t="s">
-        <v>112</v>
+        <v>22</v>
+      </c>
+      <c r="L63" s="3">
+        <v>4000</v>
       </c>
       <c r="M63" s="3" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="N63" s="3"/>
       <c r="O63" s="3"/>
@@ -3587,37 +3510,37 @@
         <v>7</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="D64" s="3">
-        <v>26032652</v>
+        <v>26031972</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>17</v>
+        <v>99</v>
       </c>
       <c r="G64" s="4">
-        <v>46101</v>
+        <v>46098</v>
       </c>
       <c r="H64" s="4">
-        <v>46101</v>
+        <v>46099</v>
       </c>
       <c r="I64" s="4">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="J64" s="3">
         <v>3</v>
       </c>
       <c r="K64" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="L64" s="3" t="s">
-        <v>113</v>
+        <v>22</v>
+      </c>
+      <c r="L64" s="3">
+        <v>1276</v>
       </c>
       <c r="M64" s="3" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="N64" s="3"/>
       <c r="O64" s="3"/>
@@ -3632,37 +3555,37 @@
         <v>7</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="D65" s="3">
-        <v>26032652</v>
+        <v>26031972</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F65" s="3" t="s">
-        <v>17</v>
+        <v>99</v>
       </c>
       <c r="G65" s="4">
-        <v>46101</v>
+        <v>46098</v>
       </c>
       <c r="H65" s="4">
-        <v>46101</v>
+        <v>46099</v>
       </c>
       <c r="I65" s="4">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="J65" s="3">
         <v>3</v>
       </c>
       <c r="K65" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="L65" s="3" t="s">
-        <v>114</v>
+        <v>22</v>
+      </c>
+      <c r="L65" s="3">
+        <v>1052</v>
       </c>
       <c r="M65" s="3" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="N65" s="3"/>
       <c r="O65" s="3"/>
@@ -3677,37 +3600,37 @@
         <v>7</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="D66" s="3">
-        <v>26032652</v>
+        <v>26031972</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>17</v>
+        <v>99</v>
       </c>
       <c r="G66" s="4">
-        <v>46101</v>
+        <v>46098</v>
       </c>
       <c r="H66" s="4">
-        <v>46101</v>
+        <v>46099</v>
       </c>
       <c r="I66" s="4">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="J66" s="3">
         <v>3</v>
       </c>
       <c r="K66" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="L66" s="3" t="s">
-        <v>115</v>
+        <v>22</v>
+      </c>
+      <c r="L66" s="3">
+        <v>1265</v>
       </c>
       <c r="M66" s="3" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="N66" s="3"/>
       <c r="O66" s="3"/>
@@ -3722,37 +3645,37 @@
         <v>7</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="D67" s="3">
-        <v>26032652</v>
+        <v>26031972</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="F67" s="3" t="s">
-        <v>17</v>
+        <v>99</v>
       </c>
       <c r="G67" s="4">
-        <v>46101</v>
+        <v>46098</v>
       </c>
       <c r="H67" s="4">
-        <v>46101</v>
+        <v>46099</v>
       </c>
       <c r="I67" s="4">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="J67" s="3">
         <v>3</v>
       </c>
       <c r="K67" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="L67" s="3" t="s">
-        <v>116</v>
+        <v>86</v>
+      </c>
+      <c r="L67" s="3">
+        <v>1424</v>
       </c>
       <c r="M67" s="3" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
@@ -3767,33 +3690,37 @@
         <v>7</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="D68" s="3">
-        <v>26032652</v>
+        <v>26031972</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F68" s="3" t="s">
-        <v>17</v>
+        <v>99</v>
       </c>
       <c r="G68" s="4">
-        <v>46101</v>
+        <v>46098</v>
       </c>
       <c r="H68" s="4">
-        <v>46101</v>
+        <v>46099</v>
       </c>
       <c r="I68" s="4">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="J68" s="3">
         <v>3</v>
       </c>
-      <c r="K68" s="3"/>
-      <c r="L68" s="3"/>
+      <c r="K68" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L68" s="3">
+        <v>1108</v>
+      </c>
       <c r="M68" s="3" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="N68" s="3"/>
       <c r="O68" s="3"/>
@@ -3808,37 +3735,37 @@
         <v>7</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="D69" s="3">
-        <v>26032652</v>
+        <v>26031972</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F69" s="3" t="s">
-        <v>17</v>
+        <v>99</v>
       </c>
       <c r="G69" s="4">
-        <v>46101</v>
+        <v>46098</v>
       </c>
       <c r="H69" s="4">
-        <v>46101</v>
+        <v>46099</v>
       </c>
       <c r="I69" s="4">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="J69" s="3">
         <v>3</v>
       </c>
       <c r="K69" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="L69" s="3" t="s">
-        <v>117</v>
+        <v>22</v>
+      </c>
+      <c r="L69" s="3">
+        <v>1263</v>
       </c>
       <c r="M69" s="3" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="N69" s="3"/>
       <c r="O69" s="3"/>
@@ -3853,37 +3780,37 @@
         <v>7</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="D70" s="3">
-        <v>26032652</v>
+        <v>26031972</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F70" s="3" t="s">
-        <v>17</v>
+        <v>99</v>
       </c>
       <c r="G70" s="4">
-        <v>46101</v>
+        <v>46098</v>
       </c>
       <c r="H70" s="4">
-        <v>46101</v>
+        <v>46099</v>
       </c>
       <c r="I70" s="4">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="J70" s="3">
         <v>3</v>
       </c>
       <c r="K70" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="L70" s="3" t="s">
-        <v>118</v>
+        <v>22</v>
+      </c>
+      <c r="L70" s="3">
+        <v>4002</v>
       </c>
       <c r="M70" s="3" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="N70" s="3"/>
       <c r="O70" s="3"/>
@@ -3898,37 +3825,37 @@
         <v>7</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="D71" s="3">
-        <v>26032652</v>
+        <v>26031972</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F71" s="3" t="s">
-        <v>17</v>
+        <v>99</v>
       </c>
       <c r="G71" s="4">
-        <v>46101</v>
+        <v>46098</v>
       </c>
       <c r="H71" s="4">
-        <v>46101</v>
+        <v>46099</v>
       </c>
       <c r="I71" s="4">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="J71" s="3">
         <v>3</v>
       </c>
       <c r="K71" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="L71" s="3" t="s">
-        <v>119</v>
+        <v>22</v>
+      </c>
+      <c r="L71" s="3">
+        <v>4004</v>
       </c>
       <c r="M71" s="3" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="N71" s="3"/>
       <c r="O71" s="3"/>
@@ -3943,37 +3870,37 @@
         <v>7</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="D72" s="3">
-        <v>26032652</v>
+        <v>26031972</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F72" s="3" t="s">
-        <v>17</v>
+        <v>99</v>
       </c>
       <c r="G72" s="4">
-        <v>46101</v>
+        <v>46098</v>
       </c>
       <c r="H72" s="4">
-        <v>46101</v>
+        <v>46099</v>
       </c>
       <c r="I72" s="4">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="J72" s="3">
         <v>3</v>
       </c>
       <c r="K72" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="L72" s="3" t="s">
-        <v>120</v>
+        <v>22</v>
+      </c>
+      <c r="L72" s="3">
+        <v>1269</v>
       </c>
       <c r="M72" s="3" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="N72" s="3"/>
       <c r="O72" s="3"/>
@@ -3988,37 +3915,37 @@
         <v>7</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="D73" s="3">
-        <v>26032652</v>
+        <v>26031972</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F73" s="3" t="s">
-        <v>17</v>
+        <v>99</v>
       </c>
       <c r="G73" s="4">
-        <v>46101</v>
+        <v>46098</v>
       </c>
       <c r="H73" s="4">
-        <v>46101</v>
+        <v>46099</v>
       </c>
       <c r="I73" s="4">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="J73" s="3">
         <v>3</v>
       </c>
       <c r="K73" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="L73" s="3" t="s">
-        <v>121</v>
+        <v>22</v>
+      </c>
+      <c r="L73" s="3">
+        <v>1187</v>
       </c>
       <c r="M73" s="3" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="N73" s="3"/>
       <c r="O73" s="3"/>
@@ -4033,41 +3960,43 @@
         <v>7</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="D74" s="3">
-        <v>26032652</v>
+        <v>26031972</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F74" s="3" t="s">
-        <v>17</v>
+        <v>99</v>
       </c>
       <c r="G74" s="4">
-        <v>46101</v>
+        <v>46098</v>
       </c>
       <c r="H74" s="4">
-        <v>46101</v>
+        <v>46099</v>
       </c>
       <c r="I74" s="4">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="J74" s="3">
         <v>3</v>
       </c>
       <c r="K74" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="L74" s="3" t="s">
-        <v>122</v>
+        <v>22</v>
+      </c>
+      <c r="L74" s="3">
+        <v>1185</v>
       </c>
       <c r="M74" s="3" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="N74" s="3"/>
       <c r="O74" s="3"/>
-      <c r="P74" s="3"/>
+      <c r="P74" s="3" t="s">
+        <v>100</v>
+      </c>
       <c r="Q74" s="3" t="b">
         <v>0</v>
       </c>
@@ -4078,37 +4007,37 @@
         <v>7</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="D75" s="3">
-        <v>26032652</v>
+        <v>26031972</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F75" s="3" t="s">
-        <v>17</v>
+        <v>99</v>
       </c>
       <c r="G75" s="4">
-        <v>46101</v>
+        <v>46098</v>
       </c>
       <c r="H75" s="4">
-        <v>46101</v>
+        <v>46099</v>
       </c>
       <c r="I75" s="4">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="J75" s="3">
         <v>3</v>
       </c>
       <c r="K75" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="L75" s="3" t="s">
-        <v>123</v>
+        <v>22</v>
+      </c>
+      <c r="L75" s="3">
+        <v>1290</v>
       </c>
       <c r="M75" s="3" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="N75" s="3"/>
       <c r="O75" s="3"/>
@@ -4120,19 +4049,19 @@
     <row r="76" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="2"/>
       <c r="B76" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="D76" s="3">
         <v>26031972</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>20</v>
+        <v>56</v>
       </c>
       <c r="F76" s="3" t="s">
-        <v>124</v>
+        <v>99</v>
       </c>
       <c r="G76" s="4">
         <v>46098</v>
@@ -4147,13 +4076,13 @@
         <v>3</v>
       </c>
       <c r="K76" s="3" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="L76" s="3">
-        <v>1422</v>
+        <v>1175</v>
       </c>
       <c r="M76" s="3" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="N76" s="3"/>
       <c r="O76" s="3"/>
@@ -4165,19 +4094,19 @@
     <row r="77" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="2"/>
       <c r="B77" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="D77" s="3">
         <v>26031972</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>28</v>
+        <v>57</v>
       </c>
       <c r="F77" s="3" t="s">
-        <v>124</v>
+        <v>99</v>
       </c>
       <c r="G77" s="4">
         <v>46098</v>
@@ -4192,13 +4121,13 @@
         <v>3</v>
       </c>
       <c r="K77" s="3" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="L77" s="3">
-        <v>1475</v>
+        <v>1060</v>
       </c>
       <c r="M77" s="3" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="N77" s="3"/>
       <c r="O77" s="3"/>
@@ -4210,19 +4139,19 @@
     <row r="78" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="2"/>
       <c r="B78" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="D78" s="3">
         <v>26031972</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="F78" s="3" t="s">
-        <v>124</v>
+        <v>99</v>
       </c>
       <c r="G78" s="4">
         <v>46098</v>
@@ -4237,13 +4166,13 @@
         <v>3</v>
       </c>
       <c r="K78" s="3" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="L78" s="3">
-        <v>4755</v>
+        <v>1066</v>
       </c>
       <c r="M78" s="3" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="N78" s="3"/>
       <c r="O78" s="3"/>
@@ -4255,19 +4184,19 @@
     <row r="79" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="2"/>
       <c r="B79" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="D79" s="3">
         <v>26031972</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>35</v>
+        <v>61</v>
       </c>
       <c r="F79" s="3" t="s">
-        <v>124</v>
+        <v>99</v>
       </c>
       <c r="G79" s="4">
         <v>46098</v>
@@ -4282,13 +4211,13 @@
         <v>3</v>
       </c>
       <c r="K79" s="3" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="L79" s="3">
-        <v>1301</v>
+        <v>1294</v>
       </c>
       <c r="M79" s="3" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="N79" s="3"/>
       <c r="O79" s="3"/>
@@ -4300,19 +4229,19 @@
     <row r="80" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="2"/>
       <c r="B80" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="D80" s="3">
         <v>26031972</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>16</v>
+        <v>101</v>
       </c>
       <c r="F80" s="3" t="s">
-        <v>124</v>
+        <v>99</v>
       </c>
       <c r="G80" s="4">
         <v>46098</v>
@@ -4327,13 +4256,13 @@
         <v>3</v>
       </c>
       <c r="K80" s="3" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="L80" s="3">
-        <v>1104</v>
+        <v>1266</v>
       </c>
       <c r="M80" s="3" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="N80" s="3"/>
       <c r="O80" s="3"/>
@@ -4344,950 +4273,402 @@
     </row>
     <row r="81" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="2"/>
-      <c r="B81" s="3">
-        <v>8</v>
-      </c>
-      <c r="C81" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D81" s="3">
-        <v>26031972</v>
-      </c>
-      <c r="E81" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F81" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="G81" s="4">
-        <v>46098</v>
-      </c>
-      <c r="H81" s="4">
-        <v>46099</v>
-      </c>
-      <c r="I81" s="4">
-        <v>46112</v>
-      </c>
-      <c r="J81" s="3">
-        <v>3</v>
-      </c>
-      <c r="K81" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="L81" s="3">
-        <v>1292</v>
-      </c>
-      <c r="M81" s="3" t="s">
-        <v>32</v>
-      </c>
+      <c r="B81" s="3"/>
+      <c r="C81" s="3"/>
+      <c r="D81" s="3"/>
+      <c r="E81" s="3"/>
+      <c r="F81" s="3"/>
+      <c r="G81" s="4"/>
+      <c r="H81" s="4"/>
+      <c r="I81" s="4"/>
+      <c r="J81" s="3"/>
+      <c r="K81" s="3"/>
+      <c r="L81" s="3"/>
+      <c r="M81" s="3"/>
       <c r="N81" s="3"/>
       <c r="O81" s="3"/>
       <c r="P81" s="3"/>
-      <c r="Q81" s="3" t="b">
-        <v>0</v>
-      </c>
+      <c r="Q81" s="3"/>
     </row>
     <row r="82" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="2"/>
-      <c r="B82" s="3">
-        <v>8</v>
-      </c>
-      <c r="C82" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D82" s="3">
-        <v>26031972</v>
-      </c>
-      <c r="E82" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="F82" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="G82" s="4">
-        <v>46098</v>
-      </c>
-      <c r="H82" s="4">
-        <v>46099</v>
-      </c>
-      <c r="I82" s="4">
-        <v>46112</v>
-      </c>
-      <c r="J82" s="3">
-        <v>3</v>
-      </c>
-      <c r="K82" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="L82" s="3">
-        <v>1342</v>
-      </c>
-      <c r="M82" s="3" t="s">
-        <v>32</v>
-      </c>
+      <c r="B82" s="3"/>
+      <c r="C82" s="3"/>
+      <c r="D82" s="3"/>
+      <c r="E82" s="3"/>
+      <c r="F82" s="3"/>
+      <c r="G82" s="4"/>
+      <c r="H82" s="4"/>
+      <c r="I82" s="4"/>
+      <c r="J82" s="3"/>
+      <c r="K82" s="3"/>
+      <c r="L82" s="3"/>
+      <c r="M82" s="3"/>
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-      <c r="Q82" s="3" t="b">
-        <v>0</v>
-      </c>
+      <c r="Q82" s="3"/>
     </row>
     <row r="83" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="2"/>
-      <c r="B83" s="3">
-        <v>8</v>
-      </c>
-      <c r="C83" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D83" s="3">
-        <v>26031972</v>
-      </c>
-      <c r="E83" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F83" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="G83" s="4">
-        <v>46098</v>
-      </c>
-      <c r="H83" s="4">
-        <v>46099</v>
-      </c>
-      <c r="I83" s="4">
-        <v>46112</v>
-      </c>
-      <c r="J83" s="3">
-        <v>3</v>
-      </c>
-      <c r="K83" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="L83" s="3">
-        <v>4265</v>
-      </c>
-      <c r="M83" s="3" t="s">
-        <v>32</v>
-      </c>
+      <c r="B83" s="3"/>
+      <c r="C83" s="3"/>
+      <c r="D83" s="3"/>
+      <c r="E83" s="3"/>
+      <c r="F83" s="3"/>
+      <c r="G83" s="4"/>
+      <c r="H83" s="4"/>
+      <c r="I83" s="4"/>
+      <c r="J83" s="3"/>
+      <c r="K83" s="3"/>
+      <c r="L83" s="3"/>
+      <c r="M83" s="3"/>
       <c r="N83" s="3"/>
       <c r="O83" s="3"/>
       <c r="P83" s="3"/>
-      <c r="Q83" s="3" t="b">
-        <v>0</v>
-      </c>
+      <c r="Q83" s="3"/>
     </row>
     <row r="84" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="2"/>
-      <c r="B84" s="3">
-        <v>8</v>
-      </c>
-      <c r="C84" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D84" s="3">
-        <v>26031972</v>
-      </c>
-      <c r="E84" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F84" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="G84" s="4">
-        <v>46098</v>
-      </c>
-      <c r="H84" s="4">
-        <v>46099</v>
-      </c>
-      <c r="I84" s="4">
-        <v>46112</v>
-      </c>
-      <c r="J84" s="3">
-        <v>3</v>
-      </c>
-      <c r="K84" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="L84" s="3">
-        <v>4000</v>
-      </c>
-      <c r="M84" s="3" t="s">
-        <v>32</v>
-      </c>
+      <c r="B84" s="3"/>
+      <c r="C84" s="3"/>
+      <c r="D84" s="3"/>
+      <c r="E84" s="3"/>
+      <c r="F84" s="3"/>
+      <c r="G84" s="4"/>
+      <c r="H84" s="4"/>
+      <c r="I84" s="4"/>
+      <c r="J84" s="3"/>
+      <c r="K84" s="3"/>
+      <c r="L84" s="3"/>
+      <c r="M84" s="3"/>
       <c r="N84" s="3"/>
       <c r="O84" s="3"/>
       <c r="P84" s="3"/>
-      <c r="Q84" s="3" t="b">
-        <v>0</v>
-      </c>
+      <c r="Q84" s="3"/>
     </row>
     <row r="85" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="2"/>
-      <c r="B85" s="3">
-        <v>8</v>
-      </c>
-      <c r="C85" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D85" s="3">
-        <v>26031972</v>
-      </c>
-      <c r="E85" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="F85" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="G85" s="4">
-        <v>46098</v>
-      </c>
-      <c r="H85" s="4">
-        <v>46099</v>
-      </c>
-      <c r="I85" s="4">
-        <v>46112</v>
-      </c>
-      <c r="J85" s="3">
-        <v>3</v>
-      </c>
-      <c r="K85" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="L85" s="3">
-        <v>1276</v>
-      </c>
-      <c r="M85" s="3" t="s">
-        <v>32</v>
-      </c>
+      <c r="B85" s="3"/>
+      <c r="C85" s="3"/>
+      <c r="D85" s="3"/>
+      <c r="E85" s="3"/>
+      <c r="F85" s="3"/>
+      <c r="G85" s="4"/>
+      <c r="H85" s="4"/>
+      <c r="I85" s="4"/>
+      <c r="J85" s="3"/>
+      <c r="K85" s="3"/>
+      <c r="L85" s="3"/>
+      <c r="M85" s="3"/>
       <c r="N85" s="3"/>
       <c r="O85" s="3"/>
       <c r="P85" s="3"/>
-      <c r="Q85" s="3" t="b">
-        <v>0</v>
-      </c>
+      <c r="Q85" s="3"/>
     </row>
     <row r="86" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="2"/>
-      <c r="B86" s="3">
-        <v>8</v>
-      </c>
-      <c r="C86" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D86" s="3">
-        <v>26031972</v>
-      </c>
-      <c r="E86" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="F86" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="G86" s="4">
-        <v>46098</v>
-      </c>
-      <c r="H86" s="4">
-        <v>46099</v>
-      </c>
-      <c r="I86" s="4">
-        <v>46112</v>
-      </c>
-      <c r="J86" s="3">
-        <v>3</v>
-      </c>
-      <c r="K86" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="L86" s="3">
-        <v>1052</v>
-      </c>
-      <c r="M86" s="3" t="s">
-        <v>32</v>
-      </c>
+      <c r="B86" s="3"/>
+      <c r="C86" s="3"/>
+      <c r="D86" s="3"/>
+      <c r="E86" s="3"/>
+      <c r="F86" s="3"/>
+      <c r="G86" s="4"/>
+      <c r="H86" s="4"/>
+      <c r="I86" s="4"/>
+      <c r="J86" s="3"/>
+      <c r="K86" s="3"/>
+      <c r="L86" s="3"/>
+      <c r="M86" s="3"/>
       <c r="N86" s="3"/>
       <c r="O86" s="3"/>
       <c r="P86" s="3"/>
-      <c r="Q86" s="3" t="b">
-        <v>0</v>
-      </c>
+      <c r="Q86" s="3"/>
     </row>
     <row r="87" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="2"/>
-      <c r="B87" s="3">
-        <v>8</v>
-      </c>
-      <c r="C87" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D87" s="3">
-        <v>26031972</v>
-      </c>
-      <c r="E87" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="F87" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="G87" s="4">
-        <v>46098</v>
-      </c>
-      <c r="H87" s="4">
-        <v>46099</v>
-      </c>
-      <c r="I87" s="4">
-        <v>46112</v>
-      </c>
-      <c r="J87" s="3">
-        <v>3</v>
-      </c>
-      <c r="K87" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="L87" s="3">
-        <v>1265</v>
-      </c>
-      <c r="M87" s="3" t="s">
-        <v>32</v>
-      </c>
+      <c r="B87" s="3"/>
+      <c r="C87" s="3"/>
+      <c r="D87" s="3"/>
+      <c r="E87" s="3"/>
+      <c r="F87" s="3"/>
+      <c r="G87" s="4"/>
+      <c r="H87" s="4"/>
+      <c r="I87" s="4"/>
+      <c r="J87" s="3"/>
+      <c r="K87" s="3"/>
+      <c r="L87" s="3"/>
+      <c r="M87" s="3"/>
       <c r="N87" s="3"/>
       <c r="O87" s="3"/>
       <c r="P87" s="3"/>
-      <c r="Q87" s="3" t="b">
-        <v>0</v>
-      </c>
+      <c r="Q87" s="3"/>
     </row>
     <row r="88" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="2"/>
-      <c r="B88" s="3">
-        <v>8</v>
-      </c>
-      <c r="C88" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D88" s="3">
-        <v>26031972</v>
-      </c>
-      <c r="E88" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="F88" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="G88" s="4">
-        <v>46098</v>
-      </c>
-      <c r="H88" s="4">
-        <v>46099</v>
-      </c>
-      <c r="I88" s="4">
-        <v>46112</v>
-      </c>
-      <c r="J88" s="3">
-        <v>3</v>
-      </c>
-      <c r="K88" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="L88" s="3">
-        <v>1424</v>
-      </c>
-      <c r="M88" s="3" t="s">
-        <v>32</v>
-      </c>
+      <c r="B88" s="3"/>
+      <c r="C88" s="3"/>
+      <c r="D88" s="3"/>
+      <c r="E88" s="3"/>
+      <c r="F88" s="3"/>
+      <c r="G88" s="4"/>
+      <c r="H88" s="4"/>
+      <c r="I88" s="4"/>
+      <c r="J88" s="3"/>
+      <c r="K88" s="3"/>
+      <c r="L88" s="3"/>
+      <c r="M88" s="3"/>
       <c r="N88" s="3"/>
       <c r="O88" s="3"/>
       <c r="P88" s="3"/>
-      <c r="Q88" s="3" t="b">
-        <v>0</v>
-      </c>
+      <c r="Q88" s="3"/>
     </row>
     <row r="89" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="2"/>
-      <c r="B89" s="3">
-        <v>8</v>
-      </c>
-      <c r="C89" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D89" s="3">
-        <v>26031972</v>
-      </c>
-      <c r="E89" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="F89" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="G89" s="4">
-        <v>46098</v>
-      </c>
-      <c r="H89" s="4">
-        <v>46099</v>
-      </c>
-      <c r="I89" s="4">
-        <v>46112</v>
-      </c>
-      <c r="J89" s="3">
-        <v>3</v>
-      </c>
-      <c r="K89" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="L89" s="3">
-        <v>1108</v>
-      </c>
-      <c r="M89" s="3" t="s">
-        <v>32</v>
-      </c>
+      <c r="B89" s="3"/>
+      <c r="C89" s="3"/>
+      <c r="D89" s="3"/>
+      <c r="E89" s="3"/>
+      <c r="F89" s="3"/>
+      <c r="G89" s="4"/>
+      <c r="H89" s="4"/>
+      <c r="I89" s="4"/>
+      <c r="J89" s="3"/>
+      <c r="K89" s="3"/>
+      <c r="L89" s="3"/>
+      <c r="M89" s="3"/>
       <c r="N89" s="3"/>
       <c r="O89" s="3"/>
       <c r="P89" s="3"/>
-      <c r="Q89" s="3" t="b">
-        <v>0</v>
-      </c>
+      <c r="Q89" s="3"/>
     </row>
     <row r="90" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="2"/>
-      <c r="B90" s="3">
-        <v>8</v>
-      </c>
-      <c r="C90" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D90" s="3">
-        <v>26031972</v>
-      </c>
-      <c r="E90" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="F90" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="G90" s="4">
-        <v>46098</v>
-      </c>
-      <c r="H90" s="4">
-        <v>46099</v>
-      </c>
-      <c r="I90" s="4">
-        <v>46112</v>
-      </c>
-      <c r="J90" s="3">
-        <v>3</v>
-      </c>
-      <c r="K90" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="L90" s="3">
-        <v>1263</v>
-      </c>
-      <c r="M90" s="3" t="s">
-        <v>32</v>
-      </c>
+      <c r="B90" s="3"/>
+      <c r="C90" s="3"/>
+      <c r="D90" s="3"/>
+      <c r="E90" s="3"/>
+      <c r="F90" s="3"/>
+      <c r="G90" s="4"/>
+      <c r="H90" s="4"/>
+      <c r="I90" s="4"/>
+      <c r="J90" s="3"/>
+      <c r="K90" s="3"/>
+      <c r="L90" s="3"/>
+      <c r="M90" s="3"/>
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-      <c r="Q90" s="3" t="b">
-        <v>0</v>
-      </c>
+      <c r="Q90" s="3"/>
     </row>
     <row r="91" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="2"/>
-      <c r="B91" s="3">
-        <v>8</v>
-      </c>
-      <c r="C91" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D91" s="3">
-        <v>26031972</v>
-      </c>
-      <c r="E91" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="F91" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="G91" s="4">
-        <v>46098</v>
-      </c>
-      <c r="H91" s="4">
-        <v>46099</v>
-      </c>
-      <c r="I91" s="4">
-        <v>46112</v>
-      </c>
-      <c r="J91" s="3">
-        <v>3</v>
-      </c>
-      <c r="K91" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="L91" s="3">
-        <v>4002</v>
-      </c>
-      <c r="M91" s="3" t="s">
-        <v>32</v>
-      </c>
+      <c r="B91" s="3"/>
+      <c r="C91" s="3"/>
+      <c r="D91" s="3"/>
+      <c r="E91" s="3"/>
+      <c r="F91" s="3"/>
+      <c r="G91" s="4"/>
+      <c r="H91" s="4"/>
+      <c r="I91" s="4"/>
+      <c r="J91" s="3"/>
+      <c r="K91" s="3"/>
+      <c r="L91" s="3"/>
+      <c r="M91" s="3"/>
       <c r="N91" s="3"/>
       <c r="O91" s="3"/>
       <c r="P91" s="3"/>
-      <c r="Q91" s="3" t="b">
-        <v>0</v>
-      </c>
+      <c r="Q91" s="3"/>
     </row>
     <row r="92" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="2"/>
-      <c r="B92" s="3">
-        <v>8</v>
-      </c>
-      <c r="C92" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D92" s="3">
-        <v>26031972</v>
-      </c>
-      <c r="E92" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="F92" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="G92" s="4">
-        <v>46098</v>
-      </c>
-      <c r="H92" s="4">
-        <v>46099</v>
-      </c>
-      <c r="I92" s="4">
-        <v>46112</v>
-      </c>
-      <c r="J92" s="3">
-        <v>3</v>
-      </c>
-      <c r="K92" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="L92" s="3">
-        <v>4004</v>
-      </c>
-      <c r="M92" s="3" t="s">
-        <v>32</v>
-      </c>
+      <c r="B92" s="3"/>
+      <c r="C92" s="3"/>
+      <c r="D92" s="3"/>
+      <c r="E92" s="3"/>
+      <c r="F92" s="3"/>
+      <c r="G92" s="4"/>
+      <c r="H92" s="4"/>
+      <c r="I92" s="4"/>
+      <c r="J92" s="3"/>
+      <c r="K92" s="3"/>
+      <c r="L92" s="3"/>
+      <c r="M92" s="3"/>
       <c r="N92" s="3"/>
       <c r="O92" s="3"/>
       <c r="P92" s="3"/>
-      <c r="Q92" s="3" t="b">
-        <v>0</v>
-      </c>
+      <c r="Q92" s="3"/>
     </row>
     <row r="93" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="2"/>
-      <c r="B93" s="3">
-        <v>8</v>
-      </c>
-      <c r="C93" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D93" s="3">
-        <v>26031972</v>
-      </c>
-      <c r="E93" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="F93" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="G93" s="4">
-        <v>46098</v>
-      </c>
-      <c r="H93" s="4">
-        <v>46099</v>
-      </c>
-      <c r="I93" s="4">
-        <v>46112</v>
-      </c>
-      <c r="J93" s="3">
-        <v>3</v>
-      </c>
-      <c r="K93" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="L93" s="3">
-        <v>1269</v>
-      </c>
-      <c r="M93" s="3" t="s">
-        <v>32</v>
-      </c>
+      <c r="B93" s="3"/>
+      <c r="C93" s="3"/>
+      <c r="D93" s="3"/>
+      <c r="E93" s="3"/>
+      <c r="F93" s="3"/>
+      <c r="G93" s="4"/>
+      <c r="H93" s="4"/>
+      <c r="I93" s="4"/>
+      <c r="J93" s="3"/>
+      <c r="K93" s="3"/>
+      <c r="L93" s="3"/>
+      <c r="M93" s="3"/>
       <c r="N93" s="3"/>
       <c r="O93" s="3"/>
       <c r="P93" s="3"/>
-      <c r="Q93" s="3" t="b">
-        <v>0</v>
-      </c>
+      <c r="Q93" s="3"/>
     </row>
     <row r="94" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="2"/>
-      <c r="B94" s="3">
-        <v>8</v>
-      </c>
-      <c r="C94" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D94" s="3">
-        <v>26031972</v>
-      </c>
-      <c r="E94" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="F94" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="G94" s="4">
-        <v>46098</v>
-      </c>
-      <c r="H94" s="4">
-        <v>46099</v>
-      </c>
-      <c r="I94" s="4">
-        <v>46112</v>
-      </c>
-      <c r="J94" s="3">
-        <v>3</v>
-      </c>
-      <c r="K94" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="L94" s="3">
-        <v>1187</v>
-      </c>
-      <c r="M94" s="3" t="s">
-        <v>32</v>
-      </c>
+      <c r="B94" s="3"/>
+      <c r="C94" s="3"/>
+      <c r="D94" s="3"/>
+      <c r="E94" s="3"/>
+      <c r="F94" s="3"/>
+      <c r="G94" s="4"/>
+      <c r="H94" s="4"/>
+      <c r="I94" s="4"/>
+      <c r="J94" s="3"/>
+      <c r="K94" s="3"/>
+      <c r="L94" s="3"/>
+      <c r="M94" s="3"/>
       <c r="N94" s="3"/>
       <c r="O94" s="3"/>
       <c r="P94" s="3"/>
-      <c r="Q94" s="3" t="b">
-        <v>0</v>
-      </c>
+      <c r="Q94" s="3"/>
     </row>
     <row r="95" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="2"/>
-      <c r="B95" s="3">
-        <v>8</v>
-      </c>
-      <c r="C95" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D95" s="3">
-        <v>26031972</v>
-      </c>
-      <c r="E95" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="F95" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="G95" s="4">
-        <v>46098</v>
-      </c>
-      <c r="H95" s="4">
-        <v>46099</v>
-      </c>
-      <c r="I95" s="4">
-        <v>46112</v>
-      </c>
-      <c r="J95" s="3">
-        <v>3</v>
-      </c>
-      <c r="K95" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="L95" s="3">
-        <v>1185</v>
-      </c>
-      <c r="M95" s="3" t="s">
-        <v>32</v>
-      </c>
+      <c r="B95" s="3"/>
+      <c r="C95" s="3"/>
+      <c r="D95" s="3"/>
+      <c r="E95" s="3"/>
+      <c r="F95" s="3"/>
+      <c r="G95" s="4"/>
+      <c r="H95" s="4"/>
+      <c r="I95" s="4"/>
+      <c r="J95" s="3"/>
+      <c r="K95" s="3"/>
+      <c r="L95" s="3"/>
+      <c r="M95" s="3"/>
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
-      <c r="P95" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="Q95" s="3" t="b">
-        <v>0</v>
-      </c>
+      <c r="P95" s="3"/>
+      <c r="Q95" s="3"/>
     </row>
     <row r="96" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="2"/>
-      <c r="B96" s="3">
-        <v>8</v>
-      </c>
-      <c r="C96" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D96" s="3">
-        <v>26031972</v>
-      </c>
-      <c r="E96" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="F96" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="G96" s="4">
-        <v>46098</v>
-      </c>
-      <c r="H96" s="4">
-        <v>46099</v>
-      </c>
-      <c r="I96" s="4">
-        <v>46112</v>
-      </c>
-      <c r="J96" s="3">
-        <v>3</v>
-      </c>
-      <c r="K96" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="L96" s="3">
-        <v>1290</v>
-      </c>
-      <c r="M96" s="3" t="s">
-        <v>32</v>
-      </c>
+      <c r="B96" s="3"/>
+      <c r="C96" s="3"/>
+      <c r="D96" s="3"/>
+      <c r="E96" s="3"/>
+      <c r="F96" s="3"/>
+      <c r="G96" s="4"/>
+      <c r="H96" s="4"/>
+      <c r="I96" s="4"/>
+      <c r="J96" s="3"/>
+      <c r="K96" s="3"/>
+      <c r="L96" s="3"/>
+      <c r="M96" s="3"/>
       <c r="N96" s="3"/>
       <c r="O96" s="3"/>
       <c r="P96" s="3"/>
-      <c r="Q96" s="3" t="b">
-        <v>0</v>
-      </c>
+      <c r="Q96" s="3"/>
     </row>
     <row r="97" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="2"/>
-      <c r="B97" s="3">
-        <v>8</v>
-      </c>
-      <c r="C97" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D97" s="3">
-        <v>26031972</v>
-      </c>
-      <c r="E97" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="F97" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="G97" s="4">
-        <v>46098</v>
-      </c>
-      <c r="H97" s="4">
-        <v>46099</v>
-      </c>
-      <c r="I97" s="4">
-        <v>46112</v>
-      </c>
-      <c r="J97" s="3">
-        <v>3</v>
-      </c>
-      <c r="K97" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="L97" s="3">
-        <v>1175</v>
-      </c>
-      <c r="M97" s="3" t="s">
-        <v>32</v>
-      </c>
+      <c r="B97" s="3"/>
+      <c r="C97" s="3"/>
+      <c r="D97" s="3"/>
+      <c r="E97" s="3"/>
+      <c r="F97" s="3"/>
+      <c r="G97" s="4"/>
+      <c r="H97" s="4"/>
+      <c r="I97" s="4"/>
+      <c r="J97" s="3"/>
+      <c r="K97" s="3"/>
+      <c r="L97" s="3"/>
+      <c r="M97" s="3"/>
       <c r="N97" s="3"/>
       <c r="O97" s="3"/>
       <c r="P97" s="3"/>
-      <c r="Q97" s="3" t="b">
-        <v>0</v>
-      </c>
+      <c r="Q97" s="3"/>
     </row>
     <row r="98" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="2"/>
-      <c r="B98" s="3">
-        <v>8</v>
-      </c>
-      <c r="C98" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D98" s="3">
-        <v>26031972</v>
-      </c>
-      <c r="E98" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="F98" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="G98" s="4">
-        <v>46098</v>
-      </c>
-      <c r="H98" s="4">
-        <v>46099</v>
-      </c>
-      <c r="I98" s="4">
-        <v>46112</v>
-      </c>
-      <c r="J98" s="3">
-        <v>3</v>
-      </c>
-      <c r="K98" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="L98" s="3">
-        <v>1060</v>
-      </c>
-      <c r="M98" s="3" t="s">
-        <v>32</v>
-      </c>
+      <c r="B98" s="3"/>
+      <c r="C98" s="3"/>
+      <c r="D98" s="3"/>
+      <c r="E98" s="3"/>
+      <c r="F98" s="3"/>
+      <c r="G98" s="4"/>
+      <c r="H98" s="4"/>
+      <c r="I98" s="4"/>
+      <c r="J98" s="3"/>
+      <c r="K98" s="3"/>
+      <c r="L98" s="3"/>
+      <c r="M98" s="3"/>
       <c r="N98" s="3"/>
       <c r="O98" s="3"/>
       <c r="P98" s="3"/>
-      <c r="Q98" s="3" t="b">
-        <v>0</v>
-      </c>
+      <c r="Q98" s="3"/>
     </row>
     <row r="99" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="2"/>
-      <c r="B99" s="3">
-        <v>8</v>
-      </c>
-      <c r="C99" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D99" s="3">
-        <v>26031972</v>
-      </c>
-      <c r="E99" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="F99" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="G99" s="4">
-        <v>46098</v>
-      </c>
-      <c r="H99" s="4">
-        <v>46099</v>
-      </c>
-      <c r="I99" s="4">
-        <v>46112</v>
-      </c>
-      <c r="J99" s="3">
-        <v>3</v>
-      </c>
-      <c r="K99" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="L99" s="3">
-        <v>1066</v>
-      </c>
-      <c r="M99" s="3" t="s">
-        <v>32</v>
-      </c>
+      <c r="B99" s="3"/>
+      <c r="C99" s="3"/>
+      <c r="D99" s="3"/>
+      <c r="E99" s="3"/>
+      <c r="F99" s="3"/>
+      <c r="G99" s="4"/>
+      <c r="H99" s="4"/>
+      <c r="I99" s="4"/>
+      <c r="J99" s="3"/>
+      <c r="K99" s="3"/>
+      <c r="L99" s="3"/>
+      <c r="M99" s="3"/>
       <c r="N99" s="3"/>
       <c r="O99" s="3"/>
       <c r="P99" s="3"/>
-      <c r="Q99" s="3" t="b">
-        <v>0</v>
-      </c>
+      <c r="Q99" s="3"/>
     </row>
     <row r="100" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="2"/>
-      <c r="B100" s="3">
-        <v>8</v>
-      </c>
-      <c r="C100" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D100" s="3">
-        <v>26031972</v>
-      </c>
-      <c r="E100" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="F100" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="G100" s="4">
-        <v>46098</v>
-      </c>
-      <c r="H100" s="4">
-        <v>46099</v>
-      </c>
-      <c r="I100" s="4">
-        <v>46112</v>
-      </c>
-      <c r="J100" s="3">
-        <v>3</v>
-      </c>
-      <c r="K100" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="L100" s="3">
-        <v>1294</v>
-      </c>
-      <c r="M100" s="3" t="s">
-        <v>32</v>
-      </c>
+      <c r="B100" s="3"/>
+      <c r="C100" s="3"/>
+      <c r="D100" s="3"/>
+      <c r="E100" s="3"/>
+      <c r="F100" s="3"/>
+      <c r="G100" s="4"/>
+      <c r="H100" s="4"/>
+      <c r="I100" s="4"/>
+      <c r="J100" s="3"/>
+      <c r="K100" s="3"/>
+      <c r="L100" s="3"/>
+      <c r="M100" s="3"/>
       <c r="N100" s="3"/>
       <c r="O100" s="3"/>
       <c r="P100" s="3"/>
-      <c r="Q100" s="3" t="b">
-        <v>0</v>
-      </c>
+      <c r="Q100" s="3"/>
     </row>
     <row r="101" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="2"/>
-      <c r="B101" s="3">
-        <v>8</v>
-      </c>
-      <c r="C101" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D101" s="3">
-        <v>26031972</v>
-      </c>
-      <c r="E101" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="F101" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="G101" s="4">
-        <v>46098</v>
-      </c>
-      <c r="H101" s="4">
-        <v>46099</v>
-      </c>
-      <c r="I101" s="4">
-        <v>46112</v>
-      </c>
-      <c r="J101" s="3">
-        <v>3</v>
-      </c>
-      <c r="K101" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="L101" s="3">
-        <v>1266</v>
-      </c>
-      <c r="M101" s="3" t="s">
-        <v>32</v>
-      </c>
+      <c r="B101" s="3"/>
+      <c r="C101" s="3"/>
+      <c r="D101" s="3"/>
+      <c r="E101" s="3"/>
+      <c r="F101" s="3"/>
+      <c r="G101" s="4"/>
+      <c r="H101" s="4"/>
+      <c r="I101" s="4"/>
+      <c r="J101" s="3"/>
+      <c r="K101" s="3"/>
+      <c r="L101" s="3"/>
+      <c r="M101" s="3"/>
       <c r="N101" s="3"/>
       <c r="O101" s="3"/>
       <c r="P101" s="3"/>
-      <c r="Q101" s="3" t="b">
-        <v>0</v>
-      </c>
+      <c r="Q101" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Pittsburgh WIP Data/WIP Data Import Template.xlsx
+++ b/Pittsburgh WIP Data/WIP Data Import Template.xlsx
@@ -1690,4 +1690,145 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100F54ED89BB92EAE4A8D085C2645895077" ma:contentTypeVersion="0" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="cb4650797810e6fb5847845c94846ae6">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="500c6692915ba10984c0aabd49f31b22">
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all/>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{573B8F31-ABB8-4212-823D-3932226CE093}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1CED187D-1828-4BCC-9DD5-49EDA2958355}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0D0670CA-0176-4E9E-9F3E-D59FDE27F9C0}"/>
 </file>
--- a/Pittsburgh WIP Data/WIP Data Import Template.xlsx
+++ b/Pittsburgh WIP Data/WIP Data Import Template.xlsx
@@ -1693,17 +1693,84 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100F54ED89BB92EAE4A8D085C2645895077" ma:contentTypeVersion="0" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="cb4650797810e6fb5847845c94846ae6">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="500c6692915ba10984c0aabd49f31b22">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100F54ED89BB92EAE4A8D085C2645895077" ma:contentTypeVersion="9" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="36c0950a3b651bcb9e0f0c750dbc94cf">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="62fc909e-fa7b-4b9e-9c51-4a8424c8313f" xmlns:ns3="2088bc9b-eb86-49b3-8eba-c8808731748f" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9639c74eb90cf937e8be4a4cd65025dc" ns2:_="" ns3:_="">
+    <xsd:import namespace="62fc909e-fa7b-4b9e-9c51-4a8424c8313f"/>
+    <xsd:import namespace="2088bc9b-eb86-49b3-8eba-c8808731748f"/>
     <xsd:element name="properties">
       <xsd:complexType>
         <xsd:sequence>
           <xsd:element name="documentManagement">
             <xsd:complexType>
-              <xsd:all/>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+              </xsd:all>
             </xsd:complexType>
           </xsd:element>
         </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="62fc909e-fa7b-4b9e-9c51-4a8424c8313f" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="11" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="55a998ee-6f6e-4d57-a444-dee5c8a083a5" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="15" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="16" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="2088bc9b-eb86-49b3-8eba-c8808731748f" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="TaxCatchAll" ma:index="14" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{30b9fb54-6ab8-432d-85bd-330831c923c3}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="2088bc9b-eb86-49b3-8eba-c8808731748f">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
       </xsd:complexType>
     </xsd:element>
   </xsd:schema>
@@ -1817,12 +1884,17 @@
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="62fc909e-fa7b-4b9e-9c51-4a8424c8313f">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="2088bc9b-eb86-49b3-8eba-c8808731748f" xsi:nil="true"/>
+  </documentManagement>
 </p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{573B8F31-ABB8-4212-823D-3932226CE093}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F6B1952F-5A65-43F8-ABF2-B6D91B9C7E8F}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
